--- a/荷量実績_20241014-20241021.xlsx
+++ b/荷量実績_20241014-20241021.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="431">
   <si>
     <t>項目名</t>
   </si>
@@ -100,12 +100,861 @@
     <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-14\31-40%\image_2024-10-14_13z02z44.jpg</t>
   </si>
   <si>
+    <t>2024/10/15</t>
+  </si>
+  <si>
+    <t>2024/10/15 06:14</t>
+  </si>
+  <si>
+    <t>2024/10/15 06:48</t>
+  </si>
+  <si>
+    <t>41-50</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\0%\image_2024-10-15_06z14z36.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\41-50%\image_2024-10-15_06z48z23.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/15 08:34</t>
+  </si>
+  <si>
+    <t>2024/10/15 08:50</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\other\image_2024-10-15_08z34z41.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\41-50%\image_2024-10-15_08z50z02.jpg</t>
+  </si>
+  <si>
+    <t>8875</t>
+  </si>
+  <si>
+    <t>2024/10/15 09:53</t>
+  </si>
+  <si>
+    <t>2024/10/15 10:06</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\other\image_2024-10-15_09z53z07.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\opening\image_2024-10-15_10z06z49.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/15 11:11</t>
+  </si>
+  <si>
+    <t>2024/10/15 11:25</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\31-40%\image_2024-10-15_11z11z10.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\0%\image_2024-10-15_11z24z51.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/15 14:04</t>
+  </si>
+  <si>
+    <t>2024/10/15 14:24</t>
+  </si>
+  <si>
+    <t>81-90</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\81-90%\image_2024-10-15_14z04z56.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\opening\image_2024-10-15_14z24z28.jpg</t>
+  </si>
+  <si>
+    <t>9648</t>
+  </si>
+  <si>
+    <t>2024/10/15 21:57</t>
+  </si>
+  <si>
+    <t>2024/10/15 22:03</t>
+  </si>
+  <si>
+    <t>11-20</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\11-20%\image_2024-10-15_21z57z31.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\31-40%\image_2024-10-15_22z03z17.jpg</t>
+  </si>
+  <si>
+    <t>0419</t>
+  </si>
+  <si>
+    <t>2024/10/15 22:48</t>
+  </si>
+  <si>
+    <t>2024/10/15 23:28</t>
+  </si>
+  <si>
+    <t>51-60</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\51-60%\image_2024-10-15_22z49z03.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\41-50%\image_2024-10-15_23z28z41.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/16</t>
+  </si>
+  <si>
+    <t>2024/10/16 00:58</t>
+  </si>
+  <si>
+    <t>2024/10/16 01:10</t>
+  </si>
+  <si>
+    <t>21-30</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\21-30%\image_2024-10-16_00z58z06.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\31-40%\image_2024-10-16_01z10z02.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/16 02:14</t>
+  </si>
+  <si>
+    <t>2024/10/16 02:23</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\other\image_2024-10-16_02z14z49.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\11-20%\image_2024-10-16_02z23z34.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/16 03:36</t>
+  </si>
+  <si>
+    <t>2024/10/16 03:50</t>
+  </si>
+  <si>
+    <t>61-70</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\other\image_2024-10-16_03z36z41.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\61-70%\image_2024-10-16_03z50z48.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/16 04:49</t>
+  </si>
+  <si>
+    <t>2024/10/16 05:08</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\51-60%\image_2024-10-16_04z49z55.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\31-40%\image_2024-10-16_05z08z24.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/16 07:23</t>
+  </si>
+  <si>
+    <t>2024/10/16 07:49</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\31-40%\image_2024-10-16_07z23z07.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\41-50%\image_2024-10-16_07z49z45.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/16 09:53</t>
+  </si>
+  <si>
+    <t>2024/10/16 10:05</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\81-90%\image_2024-10-16_09z53z59.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\closed\image_2024-10-16_10z05z20.jpg</t>
+  </si>
+  <si>
+    <t>4516</t>
+  </si>
+  <si>
+    <t>2024/10/16 11:10</t>
+  </si>
+  <si>
+    <t>2024/10/16 11:24</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\41-50%\image_2024-10-16_11z10z44.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\0%\image_2024-10-16_11z24z41.jpg</t>
+  </si>
+  <si>
+    <t>1938</t>
+  </si>
+  <si>
+    <t>2024/10/17</t>
+  </si>
+  <si>
+    <t>2024/10/17 00:44</t>
+  </si>
+  <si>
+    <t>2024/10/17 01:02</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\11-20%\image_2024-10-17_00z44z34.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\31-40%\image_2024-10-17_01z01z57.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/18</t>
+  </si>
+  <si>
+    <t>2024/10/18 00:52</t>
+  </si>
+  <si>
+    <t>2024/10/18 01:04</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\21-30%\image_2024-10-18_00z52z17.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\31-40%\image_2024-10-18_01z03z54.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/18 13:41</t>
+  </si>
+  <si>
+    <t>2024/10/18 13:48</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\41-50%\image_2024-10-18_13z41z20.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\41-50%\image_2024-10-18_13z48z42.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/18 15:18</t>
+  </si>
+  <si>
+    <t>2024/10/18 15:27</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\3\img\2024-10-18\21-30%\image_2024-10-18_15z18z57.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\3\img\2024-10-18\31-40%\image_2024-10-18_15z27z47.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/18 16:58</t>
+  </si>
+  <si>
+    <t>2024/10/18 17:05</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\3\img\2024-10-18\other\image_2024-10-18_16z58z04.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\3\img\2024-10-18\closed\image_2024-10-18_17z05z31.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/18 17:38</t>
+  </si>
+  <si>
+    <t>2024/10/18 18:23</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\3\img\2024-10-18\11-20%\image_2024-10-18_17z38z59.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\3\img\2024-10-18\11-20%\image_2024-10-18_18z23z16.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/18 21:17</t>
+  </si>
+  <si>
+    <t>2024/10/18 21:29</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-18\other\image_2024-10-18_21z17z22.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-18\closed\image_2024-10-18_21z29z28.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/19</t>
+  </si>
+  <si>
+    <t>2024/10/19 00:51</t>
+  </si>
+  <si>
+    <t>2024/10/19 01:03</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-19\11-20%\image_2024-10-19_00z51z18.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-19\31-40%\image_2024-10-19_01z03z24.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/21</t>
+  </si>
+  <si>
+    <t>2024/10/21 03:51</t>
+  </si>
+  <si>
+    <t>2024/10/21 03:58</t>
+  </si>
+  <si>
+    <t>1-10</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-21\1-10%\image_2024-10-21_03z51z49.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-21\1-10%\image_2024-10-21_03z58z21.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/21 04:37</t>
+  </si>
+  <si>
+    <t>2024/10/21 04:49</t>
+  </si>
+  <si>
+    <t>91-100</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-21\91-100%\image_2024-10-21_04z37z17.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-21\opening\image_2024-10-21_04z49z43.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/21 08:36</t>
+  </si>
+  <si>
+    <t>2024/10/21 08:41</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\3\img\2024-10-21\31-40%\image_2024-10-21_08z36z28.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\3\img\2024-10-21\31-40%\image_2024-10-21_08z40z58.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/21 10:19</t>
+  </si>
+  <si>
+    <t>2024/10/21 10:24</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-21\1-10%\image_2024-10-21_10z19z04.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-21\0%\image_2024-10-21_10z24z05.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/21 13:44</t>
+  </si>
+  <si>
+    <t>2024/10/21 13:52</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\3\img\2024-10-21\81-90%\image_2024-10-21_13z44z37.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\3\img\2024-10-21\61-70%\image_2024-10-21_13z52z20.jpg</t>
+  </si>
+  <si>
+    <t>8t常傭便1</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>岩渕</t>
+  </si>
+  <si>
+    <t>1084</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>2024/10/18 16:43</t>
+  </si>
+  <si>
+    <t>2024/10/18 16:55</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-18\41-50%\image_2024-10-18_16z43z57.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-18\0%\image_2024-10-18_16z55z02.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/21 16:41</t>
+  </si>
+  <si>
+    <t>2024/10/21 16:52</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-21\61-70%\image_2024-10-21_16z41z29.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-21\closed\image_2024-10-21_16z52z10.jpg</t>
+  </si>
+  <si>
+    <t>8t常傭便3</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>名城</t>
+  </si>
+  <si>
+    <t>2160</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>2024/10/21 09:28</t>
+  </si>
+  <si>
+    <t>2024/10/21 09:39</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-21\61-70%\image_2024-10-21_09z28z47.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-21\1-10%\image_2024-10-21_09z39z13.jpg</t>
+  </si>
+  <si>
+    <t>8t常傭便4</t>
+  </si>
+  <si>
+    <t>新家</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>2024/10/16 18:36</t>
+  </si>
+  <si>
+    <t>2024/10/16 18:41</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\11-20%\image_2024-10-16_18z36z42.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\0%\image_2024-10-16_18z41z28.jpg</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>2024/10/17 11:03</t>
+  </si>
+  <si>
+    <t>2024/10/17 11:14</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\31-40%\image_2024-10-17_11z03z47.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\0%\image_2024-10-17_11z14z20.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/17 18:33</t>
+  </si>
+  <si>
+    <t>2024/10/17 18:36</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\other\image_2024-10-17_18z33z21.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\0%\image_2024-10-17_18z36z12.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/18 11:01</t>
+  </si>
+  <si>
+    <t>2024/10/18 11:24</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\61-70%\image_2024-10-18_11z01z17.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\0%\image_2024-10-18_11z23z55.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/18 18:40</t>
+  </si>
+  <si>
+    <t>2024/10/18 18:48</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\21-30%\image_2024-10-18_18z40z21.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\0%\image_2024-10-18_18z47z52.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/21 11:06</t>
+  </si>
+  <si>
+    <t>2024/10/21 11:20</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-21\41-50%\image_2024-10-21_11z06z35.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-21\0%\image_2024-10-21_11z19z57.jpg</t>
+  </si>
+  <si>
+    <t>8t常傭便6</t>
+  </si>
+  <si>
+    <t>神谷/木村</t>
+  </si>
+  <si>
+    <t>6796</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>2024/10/19 01:13</t>
+  </si>
+  <si>
+    <t>2024/10/19 01:24</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-19\1-10%\image_2024-10-19_01z13z03.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-19\61-70%\image_2024-10-19_01z24z25.jpg</t>
+  </si>
+  <si>
+    <t>大型常傭便2</t>
+  </si>
+  <si>
+    <t>宮城/峯尾</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>2024/10/21 13:08</t>
+  </si>
+  <si>
+    <t>2024/10/21 13:23</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\3\img\2024-10-21\31-40%\image_2024-10-21_13z08z59.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\3\img\2024-10-21\11-20%\image_2024-10-21_13z22z55.jpg</t>
+  </si>
+  <si>
+    <t>豊鉄8t常傭便1</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>宮崎/野畑</t>
+  </si>
+  <si>
+    <t>9646</t>
+  </si>
+  <si>
+    <t>23:10</t>
+  </si>
+  <si>
+    <t>23:30</t>
+  </si>
+  <si>
+    <t>2024/10/18 22:31</t>
+  </si>
+  <si>
+    <t>2024/10/18 22:54</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-18\1-10%\image_2024-10-18_22z31z10.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-18\91-100%\image_2024-10-18_22z54z28.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/20</t>
+  </si>
+  <si>
+    <t>2024/10/21 12:55</t>
+  </si>
+  <si>
+    <t>2024/10/21 13:05</t>
+  </si>
+  <si>
+    <t>71-80</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-21\11-20%\image_2024-10-21_12z55z23.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-21\71-80%\image_2024-10-21_13z05z15.jpg</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>12:20</t>
+  </si>
+  <si>
+    <t>2024/10/21 11:24</t>
+  </si>
+  <si>
+    <t>2024/10/21 11:26</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-21\51-60%\image_2024-10-21_11z24z43.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-21\41-50%\image_2024-10-21_11z25z18.jpg</t>
+  </si>
+  <si>
+    <t>豊鉄8t常傭便2</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>大城/村上</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
+    <t>2024/10/16 22:02</t>
+  </si>
+  <si>
+    <t>2024/10/16 22:07</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\11-20%\image_2024-10-16_22z02z26.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\21-30%\image_2024-10-16_22z07z39.jpg</t>
+  </si>
+  <si>
+    <t>03:40</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>2024/10/17 03:36</t>
+  </si>
+  <si>
+    <t>2024/10/17 03:50</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\71-80%\image_2024-10-17_03z36z51.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\61-70%\image_2024-10-17_03z50z08.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/17 22:00</t>
+  </si>
+  <si>
+    <t>2024/10/17 22:06</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\11-20%\image_2024-10-17_22z01z01.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\21-30%\image_2024-10-17_22z06z22.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/18 03:32</t>
+  </si>
+  <si>
+    <t>2024/10/18 03:52</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\61-70%\image_2024-10-18_03z32z11.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\91-100%\image_2024-10-18_03z52z02.jpg</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>2024/10/18 18:03</t>
+  </si>
+  <si>
+    <t>2024/10/18 18:32</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-18\1-10%\image_2024-10-18_18z03z10.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-18\0%\image_2024-10-18_18z31z58.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/18 22:08</t>
+  </si>
+  <si>
+    <t>2024/10/18 22:14</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\11-20%\image_2024-10-18_22z08z40.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\31-40%\image_2024-10-18_22z14z04.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/19 03:27</t>
+  </si>
+  <si>
+    <t>2024/10/19 03:38</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-19\31-40%\image_2024-10-19_03z27z17.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-19\41-50%\image_2024-10-19_03z38z49.jpg</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>2024/10/21 10:26</t>
+  </si>
+  <si>
+    <t>2024/10/21 10:50</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-21\91-100%\image_2024-10-21_10z26z29.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-21\91-100%\image_2024-10-21_10z50z32.jpg</t>
+  </si>
+  <si>
+    <t>豊鉄8t常傭便3</t>
+  </si>
+  <si>
+    <t>阿部/与那嶺</t>
+  </si>
+  <si>
+    <t>9647</t>
+  </si>
+  <si>
+    <t>00:40</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>2024/10/19 00:06</t>
+  </si>
+  <si>
+    <t>2024/10/19 00:27</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-19\11-20%\image_2024-10-19_00z06z05.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-19\61-70%\image_2024-10-19_00z27z13.jpg</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>2024/10/21 06:01</t>
+  </si>
+  <si>
+    <t>2024/10/21 06:42</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-21\0%\image_2024-10-21_06z01z24.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-21\91-100%\image_2024-10-21_06z42z44.jpg</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>2024/10/21 13:14</t>
+  </si>
+  <si>
+    <t>2024/10/21 13:34</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-21\41-50%\image_2024-10-21_13z14z51.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-21\41-50%\image_2024-10-21_13z34z23.jpg</t>
+  </si>
+  <si>
     <t>豊鉄大型常傭便1</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>結城/川西</t>
   </si>
   <si>
@@ -124,36 +973,12 @@
     <t>2024/10/15 05:09</t>
   </si>
   <si>
-    <t>61-70</t>
-  </si>
-  <si>
     <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\61-70%\image_2024-10-15_04z53z47.jpg</t>
   </si>
   <si>
     <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\31-40%\image_2024-10-15_05z09z39.jpg</t>
   </si>
   <si>
-    <t>2024/10/15</t>
-  </si>
-  <si>
-    <t>2024/10/15 06:14</t>
-  </si>
-  <si>
-    <t>2024/10/15 06:48</t>
-  </si>
-  <si>
-    <t>41-50</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\0%\image_2024-10-15_06z14z36.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\41-50%\image_2024-10-15_06z48z23.jpg</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>08:00</t>
   </si>
   <si>
@@ -172,63 +997,6 @@
     <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\41-50%\image_2024-10-15_07z33z03.jpg</t>
   </si>
   <si>
-    <t>2024/10/15 08:34</t>
-  </si>
-  <si>
-    <t>2024/10/15 08:50</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\other\image_2024-10-15_08z34z41.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\41-50%\image_2024-10-15_08z50z02.jpg</t>
-  </si>
-  <si>
-    <t>8875</t>
-  </si>
-  <si>
-    <t>2024/10/15 09:53</t>
-  </si>
-  <si>
-    <t>2024/10/15 10:06</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\other\image_2024-10-15_09z53z07.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\opening\image_2024-10-15_10z06z49.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/15 11:11</t>
-  </si>
-  <si>
-    <t>2024/10/15 11:25</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\31-40%\image_2024-10-15_11z11z10.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\0%\image_2024-10-15_11z24z51.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/15 14:04</t>
-  </si>
-  <si>
-    <t>2024/10/15 14:24</t>
-  </si>
-  <si>
-    <t>81-90</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\81-90%\image_2024-10-15_14z04z56.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\opening\image_2024-10-15_14z24z28.jpg</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>16:50</t>
   </si>
   <si>
@@ -247,147 +1015,153 @@
     <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\41-50%\image_2024-10-15_17z11z43.jpg</t>
   </si>
   <si>
-    <t>9648</t>
-  </si>
-  <si>
-    <t>2024/10/15 21:57</t>
-  </si>
-  <si>
-    <t>2024/10/15 22:03</t>
-  </si>
-  <si>
-    <t>11-20</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\11-20%\image_2024-10-15_21z57z31.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\31-40%\image_2024-10-15_22z03z17.jpg</t>
-  </si>
-  <si>
-    <t>0419</t>
-  </si>
-  <si>
-    <t>2024/10/15 22:48</t>
-  </si>
-  <si>
-    <t>2024/10/15 23:28</t>
-  </si>
-  <si>
-    <t>51-60</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\51-60%\image_2024-10-15_22z49z03.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-15\41-50%\image_2024-10-15_23z28z41.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/16</t>
-  </si>
-  <si>
-    <t>2024/10/16 00:58</t>
-  </si>
-  <si>
-    <t>2024/10/16 01:10</t>
-  </si>
-  <si>
-    <t>21-30</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\21-30%\image_2024-10-16_00z58z06.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\31-40%\image_2024-10-16_01z10z02.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/16 02:14</t>
-  </si>
-  <si>
-    <t>2024/10/16 02:23</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\other\image_2024-10-16_02z14z49.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\11-20%\image_2024-10-16_02z23z34.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/16 03:36</t>
-  </si>
-  <si>
-    <t>2024/10/16 03:50</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\other\image_2024-10-16_03z36z41.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\61-70%\image_2024-10-16_03z50z48.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/16 04:49</t>
-  </si>
-  <si>
-    <t>2024/10/16 05:08</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\51-60%\image_2024-10-16_04z49z55.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\31-40%\image_2024-10-16_05z08z24.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/16 07:23</t>
-  </si>
-  <si>
-    <t>2024/10/16 07:49</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\31-40%\image_2024-10-16_07z23z07.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\41-50%\image_2024-10-16_07z49z45.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/16 09:53</t>
-  </si>
-  <si>
-    <t>2024/10/16 10:05</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\81-90%\image_2024-10-16_09z53z59.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\closed\image_2024-10-16_10z05z20.jpg</t>
-  </si>
-  <si>
-    <t>4516</t>
-  </si>
-  <si>
-    <t>2024/10/16 11:10</t>
-  </si>
-  <si>
-    <t>2024/10/16 11:24</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\41-50%\image_2024-10-16_11z10z44.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\0%\image_2024-10-16_11z24z41.jpg</t>
+    <t>7</t>
+  </si>
+  <si>
+    <t>2024/10/16 17:01</t>
+  </si>
+  <si>
+    <t>2024/10/16 17:18</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\other\image_2024-10-16_17z01z33.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\41-50%\image_2024-10-16_17z18z20.jpg</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>23:20</t>
+  </si>
+  <si>
+    <t>23:50</t>
+  </si>
+  <si>
+    <t>2024/10/16 22:48</t>
+  </si>
+  <si>
+    <t>2024/10/16 23:21</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\41-50%\image_2024-10-16_22z48z29.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\opening\image_2024-10-16_23z21z58.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/17 04:50</t>
+  </si>
+  <si>
+    <t>2024/10/17 05:03</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\61-70%\image_2024-10-17_04z50z06.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\31-40%\image_2024-10-17_05z03z03.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/17 07:15</t>
+  </si>
+  <si>
+    <t>2024/10/17 07:38</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\31-40%\image_2024-10-17_07z15z24.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\41-50%\image_2024-10-17_07z38z00.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/17 16:51</t>
+  </si>
+  <si>
+    <t>2024/10/17 17:13</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\51-60%\image_2024-10-17_16z51z28.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\41-50%\image_2024-10-17_17z13z27.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/17 22:50</t>
+  </si>
+  <si>
+    <t>2024/10/17 23:32</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\41-50%\image_2024-10-17_22z50z07.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\71-80%\image_2024-10-17_23z32z10.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/18 04:51</t>
+  </si>
+  <si>
+    <t>2024/10/18 05:04</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\61-70%\image_2024-10-18_04z51z17.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\31-40%\image_2024-10-18_05z04z31.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/18 07:35</t>
+  </si>
+  <si>
+    <t>2024/10/18 07:56</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\1-10%\image_2024-10-18_07z35z48.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\61-70%\image_2024-10-18_07z56z21.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/18 16:38</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\61-70%\image_2024-10-18_16z38z49.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\51-60%\image_2024-10-18_17z05z13.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/18 22:48</t>
+  </si>
+  <si>
+    <t>2024/10/18 23:20</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\31-40%\image_2024-10-18_22z48z59.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\opening\image_2024-10-18_23z20z02.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/21 07:31</t>
+  </si>
+  <si>
+    <t>2024/10/21 07:41</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-21\0%\image_2024-10-21_07z31z18.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-21\opening\image_2024-10-21_07z41z44.jpg</t>
   </si>
   <si>
     <t>豊鉄大型常傭便3</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>仲本/伊地知</t>
   </si>
   <si>
-    <t>14:10</t>
-  </si>
-  <si>
     <t>14:30</t>
   </si>
   <si>
@@ -403,111 +1177,6 @@
     <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\opening\image_2024-10-16_14z22z52.jpg</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>2024/10/16 17:01</t>
-  </si>
-  <si>
-    <t>2024/10/16 17:18</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\other\image_2024-10-16_17z01z33.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\41-50%\image_2024-10-16_17z18z20.jpg</t>
-  </si>
-  <si>
-    <t>8t常傭便4</t>
-  </si>
-  <si>
-    <t>新家</t>
-  </si>
-  <si>
-    <t>18:25</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>2024/10/16 18:36</t>
-  </si>
-  <si>
-    <t>2024/10/16 18:41</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\11-20%\image_2024-10-16_18z36z42.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\0%\image_2024-10-16_18z41z28.jpg</t>
-  </si>
-  <si>
-    <t>豊鉄8t常傭便2</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>大城/村上</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>22:40</t>
-  </si>
-  <si>
-    <t>2024/10/16 22:02</t>
-  </si>
-  <si>
-    <t>2024/10/16 22:07</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\11-20%\image_2024-10-16_22z02z26.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\21-30%\image_2024-10-16_22z07z39.jpg</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>23:20</t>
-  </si>
-  <si>
-    <t>23:50</t>
-  </si>
-  <si>
-    <t>2024/10/16 22:48</t>
-  </si>
-  <si>
-    <t>2024/10/16 23:21</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\41-50%\image_2024-10-16_22z48z29.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-16\opening\image_2024-10-16_23z21z58.jpg</t>
-  </si>
-  <si>
-    <t>1938</t>
-  </si>
-  <si>
-    <t>2024/10/17</t>
-  </si>
-  <si>
-    <t>2024/10/17 00:44</t>
-  </si>
-  <si>
-    <t>2024/10/17 01:02</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\11-20%\image_2024-10-17_00z44z34.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\31-40%\image_2024-10-17_01z01z57.jpg</t>
-  </si>
-  <si>
     <t>02:40</t>
   </si>
   <si>
@@ -526,57 +1195,6 @@
     <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\21-30%\image_2024-10-17_02z03z43.jpg</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>03:40</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>2024/10/17 03:36</t>
-  </si>
-  <si>
-    <t>2024/10/17 03:50</t>
-  </si>
-  <si>
-    <t>71-80</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\71-80%\image_2024-10-17_03z36z51.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\61-70%\image_2024-10-17_03z50z08.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/17 04:50</t>
-  </si>
-  <si>
-    <t>2024/10/17 05:03</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\61-70%\image_2024-10-17_04z50z06.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\31-40%\image_2024-10-17_05z03z03.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/17 07:15</t>
-  </si>
-  <si>
-    <t>2024/10/17 07:38</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\31-40%\image_2024-10-17_07z15z24.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\41-50%\image_2024-10-17_07z38z00.jpg</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
     <t>10:20</t>
   </si>
   <si>
@@ -592,102 +1210,18 @@
     <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\opening\image_2024-10-17_10z00z01.jpg</t>
   </si>
   <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>2024/10/17 11:03</t>
-  </si>
-  <si>
-    <t>2024/10/17 11:14</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\31-40%\image_2024-10-17_11z03z47.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\0%\image_2024-10-17_11z14z20.jpg</t>
-  </si>
-  <si>
     <t>2024/10/17 14:00</t>
   </si>
   <si>
     <t>2024/10/17 14:21</t>
   </si>
   <si>
-    <t>91-100</t>
-  </si>
-  <si>
     <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\91-100%\image_2024-10-17_14z01z00.jpg</t>
   </si>
   <si>
     <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\opening\image_2024-10-17_14z21z41.jpg</t>
   </si>
   <si>
-    <t>2024/10/17 16:51</t>
-  </si>
-  <si>
-    <t>2024/10/17 17:13</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\51-60%\image_2024-10-17_16z51z28.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\41-50%\image_2024-10-17_17z13z27.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/17 18:33</t>
-  </si>
-  <si>
-    <t>2024/10/17 18:36</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\other\image_2024-10-17_18z33z21.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\0%\image_2024-10-17_18z36z12.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/17 22:00</t>
-  </si>
-  <si>
-    <t>2024/10/17 22:06</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\11-20%\image_2024-10-17_22z01z01.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\21-30%\image_2024-10-17_22z06z22.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/17 22:50</t>
-  </si>
-  <si>
-    <t>2024/10/17 23:32</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\41-50%\image_2024-10-17_22z50z07.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-17\71-80%\image_2024-10-17_23z32z10.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/18</t>
-  </si>
-  <si>
-    <t>2024/10/18 00:52</t>
-  </si>
-  <si>
-    <t>2024/10/18 01:04</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\21-30%\image_2024-10-18_00z52z17.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\31-40%\image_2024-10-18_01z03z54.jpg</t>
-  </si>
-  <si>
     <t>2024/10/18 02:07</t>
   </si>
   <si>
@@ -700,45 +1234,6 @@
     <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\21-30%\image_2024-10-18_02z11z54.jpg</t>
   </si>
   <si>
-    <t>2024/10/18 03:32</t>
-  </si>
-  <si>
-    <t>2024/10/18 03:52</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\61-70%\image_2024-10-18_03z32z11.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\91-100%\image_2024-10-18_03z52z02.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/18 04:51</t>
-  </si>
-  <si>
-    <t>2024/10/18 05:04</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\61-70%\image_2024-10-18_04z51z17.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\31-40%\image_2024-10-18_05z04z31.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/18 07:35</t>
-  </si>
-  <si>
-    <t>2024/10/18 07:56</t>
-  </si>
-  <si>
-    <t>1-10</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\1-10%\image_2024-10-18_07z35z48.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\61-70%\image_2024-10-18_07z56z21.jpg</t>
-  </si>
-  <si>
     <t>2024/10/18 09:49</t>
   </si>
   <si>
@@ -751,30 +1246,6 @@
     <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\opening\image_2024-10-18_10z00z30.jpg</t>
   </si>
   <si>
-    <t>2024/10/18 11:01</t>
-  </si>
-  <si>
-    <t>2024/10/18 11:24</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\61-70%\image_2024-10-18_11z01z17.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\0%\image_2024-10-18_11z23z55.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/18 13:41</t>
-  </si>
-  <si>
-    <t>2024/10/18 13:48</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\41-50%\image_2024-10-18_13z41z20.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\41-50%\image_2024-10-18_13z48z42.jpg</t>
-  </si>
-  <si>
     <t>2024/10/18 13:59</t>
   </si>
   <si>
@@ -787,237 +1258,6 @@
     <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\opening\image_2024-10-18_14z15z45.jpg</t>
   </si>
   <si>
-    <t>2024/10/18 15:18</t>
-  </si>
-  <si>
-    <t>2024/10/18 15:27</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\3\img\2024-10-18\21-30%\image_2024-10-18_15z18z57.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\3\img\2024-10-18\31-40%\image_2024-10-18_15z27z47.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/18 16:38</t>
-  </si>
-  <si>
-    <t>2024/10/18 17:05</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\61-70%\image_2024-10-18_16z38z49.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\51-60%\image_2024-10-18_17z05z13.jpg</t>
-  </si>
-  <si>
-    <t>8t常傭便1</t>
-  </si>
-  <si>
-    <t>岩渕</t>
-  </si>
-  <si>
-    <t>1084</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>17:20</t>
-  </si>
-  <si>
-    <t>2024/10/18 16:43</t>
-  </si>
-  <si>
-    <t>2024/10/18 16:55</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-18\41-50%\image_2024-10-18_16z43z57.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-18\0%\image_2024-10-18_16z55z02.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/18 16:58</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\3\img\2024-10-18\other\image_2024-10-18_16z58z04.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\3\img\2024-10-18\closed\image_2024-10-18_17z05z31.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/18 17:38</t>
-  </si>
-  <si>
-    <t>2024/10/18 18:23</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\3\img\2024-10-18\11-20%\image_2024-10-18_17z38z59.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\3\img\2024-10-18\11-20%\image_2024-10-18_18z23z16.jpg</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>2024/10/18 18:03</t>
-  </si>
-  <si>
-    <t>2024/10/18 18:32</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-18\1-10%\image_2024-10-18_18z03z10.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-18\0%\image_2024-10-18_18z31z58.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/18 18:40</t>
-  </si>
-  <si>
-    <t>2024/10/18 18:48</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\21-30%\image_2024-10-18_18z40z21.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\0%\image_2024-10-18_18z47z52.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/18 21:17</t>
-  </si>
-  <si>
-    <t>2024/10/18 21:29</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-18\other\image_2024-10-18_21z17z22.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-18\closed\image_2024-10-18_21z29z28.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/18 22:08</t>
-  </si>
-  <si>
-    <t>2024/10/18 22:14</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\11-20%\image_2024-10-18_22z08z40.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\31-40%\image_2024-10-18_22z14z04.jpg</t>
-  </si>
-  <si>
-    <t>豊鉄8t常傭便1</t>
-  </si>
-  <si>
-    <t>宮崎/野畑</t>
-  </si>
-  <si>
-    <t>9646</t>
-  </si>
-  <si>
-    <t>23:10</t>
-  </si>
-  <si>
-    <t>23:30</t>
-  </si>
-  <si>
-    <t>2024/10/18 22:31</t>
-  </si>
-  <si>
-    <t>2024/10/18 22:54</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-18\1-10%\image_2024-10-18_22z31z10.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-18\91-100%\image_2024-10-18_22z54z28.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/18 22:48</t>
-  </si>
-  <si>
-    <t>2024/10/18 23:20</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\31-40%\image_2024-10-18_22z48z59.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-18\opening\image_2024-10-18_23z20z02.jpg</t>
-  </si>
-  <si>
-    <t>豊鉄8t常傭便3</t>
-  </si>
-  <si>
-    <t>阿部/与那嶺</t>
-  </si>
-  <si>
-    <t>9647</t>
-  </si>
-  <si>
-    <t>00:40</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>2024/10/19 00:06</t>
-  </si>
-  <si>
-    <t>2024/10/19 00:27</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-19\11-20%\image_2024-10-19_00z06z05.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-19\61-70%\image_2024-10-19_00z27z13.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/19</t>
-  </si>
-  <si>
-    <t>2024/10/19 00:51</t>
-  </si>
-  <si>
-    <t>2024/10/19 01:03</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-19\11-20%\image_2024-10-19_00z51z18.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-19\31-40%\image_2024-10-19_01z03z24.jpg</t>
-  </si>
-  <si>
-    <t>8t常傭便6</t>
-  </si>
-  <si>
-    <t>神谷/木村</t>
-  </si>
-  <si>
-    <t>6796</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>2024/10/19 01:13</t>
-  </si>
-  <si>
-    <t>2024/10/19 01:24</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-19\1-10%\image_2024-10-19_01z13z03.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-19\61-70%\image_2024-10-19_01z24z25.jpg</t>
-  </si>
-  <si>
     <t>2024/10/19 02:01</t>
   </si>
   <si>
@@ -1030,111 +1270,6 @@
     <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-19\31-40%\image_2024-10-19_02z07z37.jpg</t>
   </si>
   <si>
-    <t>2024/10/19 03:27</t>
-  </si>
-  <si>
-    <t>2024/10/19 03:38</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-19\31-40%\image_2024-10-19_03z27z17.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-19\41-50%\image_2024-10-19_03z38z49.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/21</t>
-  </si>
-  <si>
-    <t>2024/10/21 03:51</t>
-  </si>
-  <si>
-    <t>2024/10/21 03:58</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-21\1-10%\image_2024-10-21_03z51z49.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-21\1-10%\image_2024-10-21_03z58z21.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/21 04:37</t>
-  </si>
-  <si>
-    <t>2024/10/21 04:49</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-21\91-100%\image_2024-10-21_04z37z17.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-21\opening\image_2024-10-21_04z49z43.jpg</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>2024/10/21 06:01</t>
-  </si>
-  <si>
-    <t>2024/10/21 06:42</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-21\0%\image_2024-10-21_06z01z24.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-21\91-100%\image_2024-10-21_06z42z44.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/21 07:31</t>
-  </si>
-  <si>
-    <t>2024/10/21 07:41</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-21\0%\image_2024-10-21_07z31z18.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-21\opening\image_2024-10-21_07z41z44.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/21 08:36</t>
-  </si>
-  <si>
-    <t>2024/10/21 08:41</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\3\img\2024-10-21\31-40%\image_2024-10-21_08z36z28.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\3\img\2024-10-21\31-40%\image_2024-10-21_08z40z58.jpg</t>
-  </si>
-  <si>
-    <t>8t常傭便3</t>
-  </si>
-  <si>
-    <t>名城</t>
-  </si>
-  <si>
-    <t>2160</t>
-  </si>
-  <si>
-    <t>09:40</t>
-  </si>
-  <si>
-    <t>2024/10/21 09:28</t>
-  </si>
-  <si>
-    <t>2024/10/21 09:39</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-21\61-70%\image_2024-10-21_09z28z47.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-21\1-10%\image_2024-10-21_09z39z13.jpg</t>
-  </si>
-  <si>
     <t>2024/10/21 09:37</t>
   </si>
   <si>
@@ -1147,129 +1282,6 @@
     <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-21\11-20%\image_2024-10-21_09z41z55.jpg</t>
   </si>
   <si>
-    <t>2024/10/21 10:19</t>
-  </si>
-  <si>
-    <t>2024/10/21 10:24</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-21\1-10%\image_2024-10-21_10z19z04.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-21\0%\image_2024-10-21_10z24z05.jpg</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>2024/10/21 10:26</t>
-  </si>
-  <si>
-    <t>2024/10/21 10:50</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-21\91-100%\image_2024-10-21_10z26z29.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-21\91-100%\image_2024-10-21_10z50z32.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/21 11:06</t>
-  </si>
-  <si>
-    <t>2024/10/21 11:20</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-21\41-50%\image_2024-10-21_11z06z35.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-21\0%\image_2024-10-21_11z19z57.jpg</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>12:20</t>
-  </si>
-  <si>
-    <t>2024/10/20</t>
-  </si>
-  <si>
-    <t>2024/10/21 11:24</t>
-  </si>
-  <si>
-    <t>2024/10/21 11:26</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-21\51-60%\image_2024-10-21_11z24z43.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-21\41-50%\image_2024-10-21_11z25z18.jpg</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>2024/10/21 12:55</t>
-  </si>
-  <si>
-    <t>2024/10/21 13:05</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-21\11-20%\image_2024-10-21_12z55z23.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-21\71-80%\image_2024-10-21_13z05z15.jpg</t>
-  </si>
-  <si>
-    <t>大型常傭便2</t>
-  </si>
-  <si>
-    <t>宮城/峯尾</t>
-  </si>
-  <si>
-    <t>2024/10/21 13:08</t>
-  </si>
-  <si>
-    <t>2024/10/21 13:23</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\3\img\2024-10-21\31-40%\image_2024-10-21_13z08z59.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\3\img\2024-10-21\11-20%\image_2024-10-21_13z22z55.jpg</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>2024/10/21 13:14</t>
-  </si>
-  <si>
-    <t>2024/10/21 13:34</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-21\41-50%\image_2024-10-21_13z14z51.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\1\img\2024-10-21\41-50%\image_2024-10-21_13z34z23.jpg</t>
-  </si>
-  <si>
-    <t>2024/10/21 13:44</t>
-  </si>
-  <si>
-    <t>2024/10/21 13:52</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\3\img\2024-10-21\81-90%\image_2024-10-21_13z44z37.jpg</t>
-  </si>
-  <si>
-    <t>\\192.168.1.166\share\iot\SyncBace\3\img\2024-10-21\61-70%\image_2024-10-21_13z52z20.jpg</t>
-  </si>
-  <si>
     <t>2024/10/21 13:51</t>
   </si>
   <si>
@@ -1280,6 +1292,24 @@
   </si>
   <si>
     <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-21\1-10%\image_2024-10-21_14z07z20.jpg</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>16:40</t>
+  </si>
+  <si>
+    <t>2024/10/21 16:02</t>
+  </si>
+  <si>
+    <t>2024/10/21 16:08</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-21\41-50%\image_2024-10-21_16z02z10.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-21\71-80%\image_2024-10-21_16z08z46.jpg</t>
   </si>
 </sst>
 </file>
@@ -1354,7 +1384,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1453,49 +1483,49 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="0">
+        <v>2</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="J3" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="K3" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="0">
-        <v>2</v>
-      </c>
-      <c r="E3" s="0" t="s">
+      <c r="L3" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="0" t="s">
+      <c r="N3" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="O3" s="0" t="s">
         <v>32</v>
-      </c>
-      <c r="I3" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="M3" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="O3" s="0" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -1524,72 +1554,72 @@
         <v>19</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="J4" s="0" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="K4" s="0" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L4" s="0" t="s">
         <v>19</v>
       </c>
       <c r="M4" s="0" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="N4" s="0" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="O4" s="0" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="0">
+        <v>2</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="0">
-        <v>2</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="H5" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" s="0" t="s">
-        <v>21</v>
-      </c>
       <c r="J5" s="0" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="L5" s="0" t="s">
         <v>19</v>
       </c>
       <c r="M5" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="N5" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="O5" s="0" t="s">
         <v>41</v>
-      </c>
-      <c r="N5" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="O5" s="0" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="6">
@@ -1618,25 +1648,25 @@
         <v>19</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="J6" s="0" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="K6" s="0" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="L6" s="0" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M6" s="0" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="N6" s="0" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="O6" s="0" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -1653,10 +1683,10 @@
         <v>2</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="G7" s="0" t="s">
         <v>19</v>
@@ -1665,25 +1695,25 @@
         <v>19</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="J7" s="0" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="K7" s="0" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="L7" s="0" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="M7" s="0" t="s">
         <v>19</v>
       </c>
       <c r="N7" s="0" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="O7" s="0" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -1700,10 +1730,10 @@
         <v>2</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="G8" s="0" t="s">
         <v>19</v>
@@ -1712,25 +1742,25 @@
         <v>19</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="J8" s="0" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="K8" s="0" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="L8" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="M8" s="0" t="s">
-        <v>19</v>
-      </c>
       <c r="N8" s="0" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="O8" s="0" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9">
@@ -1747,10 +1777,10 @@
         <v>2</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G9" s="0" t="s">
         <v>19</v>
@@ -1759,72 +1789,72 @@
         <v>19</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="J9" s="0" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="K9" s="0" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="L9" s="0" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="M9" s="0" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="N9" s="0" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="O9" s="0" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D10" s="0">
         <v>2</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="J10" s="0" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="K10" s="0" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="L10" s="0" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="M10" s="0" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="N10" s="0" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="O10" s="0" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11">
@@ -1841,10 +1871,10 @@
         <v>2</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="G11" s="0" t="s">
         <v>19</v>
@@ -1853,25 +1883,25 @@
         <v>19</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="J11" s="0" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="K11" s="0" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="L11" s="0" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="M11" s="0" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="N11" s="0" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="O11" s="0" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12">
@@ -1888,10 +1918,10 @@
         <v>2</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="G12" s="0" t="s">
         <v>19</v>
@@ -1900,25 +1930,25 @@
         <v>19</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="J12" s="0" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="K12" s="0" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="L12" s="0" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="M12" s="0" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="N12" s="0" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="O12" s="0" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">
@@ -1935,10 +1965,10 @@
         <v>2</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="G13" s="0" t="s">
         <v>19</v>
@@ -1947,25 +1977,25 @@
         <v>19</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J13" s="0" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K13" s="0" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="L13" s="0" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="M13" s="0" t="s">
         <v>24</v>
       </c>
       <c r="N13" s="0" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="O13" s="0" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14">
@@ -1982,10 +2012,10 @@
         <v>2</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G14" s="0" t="s">
         <v>19</v>
@@ -1994,25 +2024,25 @@
         <v>19</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J14" s="0" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K14" s="0" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="L14" s="0" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M14" s="0" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="N14" s="0" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="O14" s="0" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15">
@@ -2029,10 +2059,10 @@
         <v>2</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="G15" s="0" t="s">
         <v>19</v>
@@ -2041,25 +2071,25 @@
         <v>19</v>
       </c>
       <c r="I15" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="J15" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="K15" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="L15" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="M15" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="N15" s="0" t="s">
         <v>88</v>
       </c>
-      <c r="J15" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="K15" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="L15" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="M15" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="N15" s="0" t="s">
-        <v>100</v>
-      </c>
       <c r="O15" s="0" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16">
@@ -2076,10 +2106,10 @@
         <v>2</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G16" s="0" t="s">
         <v>19</v>
@@ -2088,25 +2118,25 @@
         <v>19</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="J16" s="0" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="K16" s="0" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="L16" s="0" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="M16" s="0" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="N16" s="0" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="O16" s="0" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17">
@@ -2123,10 +2153,10 @@
         <v>2</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G17" s="0" t="s">
         <v>19</v>
@@ -2135,25 +2165,25 @@
         <v>19</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="J17" s="0" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="K17" s="0" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="L17" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="M17" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="M17" s="0" t="s">
-        <v>41</v>
-      </c>
       <c r="N17" s="0" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="O17" s="0" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18">
@@ -2170,10 +2200,10 @@
         <v>2</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="G18" s="0" t="s">
         <v>19</v>
@@ -2182,25 +2212,25 @@
         <v>19</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="J18" s="0" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="K18" s="0" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="L18" s="0" t="s">
         <v>66</v>
       </c>
       <c r="M18" s="0" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="N18" s="0" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="O18" s="0" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19">
@@ -2217,10 +2247,10 @@
         <v>2</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="G19" s="0" t="s">
         <v>19</v>
@@ -2229,260 +2259,260 @@
         <v>19</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="J19" s="0" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="K19" s="0" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="L19" s="0" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="M19" s="0" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="N19" s="0" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="O19" s="0" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>119</v>
+        <v>19</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>121</v>
+        <v>19</v>
       </c>
       <c r="D20" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>123</v>
+        <v>19</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="J20" s="0" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="K20" s="0" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="L20" s="0" t="s">
         <v>66</v>
       </c>
       <c r="M20" s="0" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="N20" s="0" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="O20" s="0" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>128</v>
+        <v>19</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D21" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="J21" s="0" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="K21" s="0" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="L21" s="0" t="s">
         <v>19</v>
       </c>
       <c r="M21" s="0" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="N21" s="0" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="O21" s="0" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>133</v>
+        <v>19</v>
       </c>
       <c r="B22" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="0">
+        <v>3</v>
+      </c>
+      <c r="E22" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="J22" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="K22" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="L22" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="M22" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="N22" s="0" t="s">
         <v>120</v>
       </c>
-      <c r="C22" s="0" t="s">
-        <v>134</v>
-      </c>
-      <c r="D22" s="0">
-        <v>2</v>
-      </c>
-      <c r="E22" s="0" t="s">
-        <v>114</v>
-      </c>
-      <c r="F22" s="0" t="s">
-        <v>114</v>
-      </c>
-      <c r="G22" s="0" t="s">
-        <v>135</v>
-      </c>
-      <c r="H22" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="I22" s="0" t="s">
-        <v>88</v>
-      </c>
-      <c r="J22" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="K22" s="0" t="s">
-        <v>138</v>
-      </c>
-      <c r="L22" s="0" t="s">
-        <v>79</v>
-      </c>
-      <c r="M22" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="N22" s="0" t="s">
-        <v>139</v>
-      </c>
       <c r="O22" s="0" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>141</v>
+        <v>19</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>143</v>
+        <v>19</v>
       </c>
       <c r="D23" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>144</v>
+        <v>19</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>145</v>
+        <v>19</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="J23" s="0" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="K23" s="0" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="L23" s="0" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="M23" s="0" t="s">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="N23" s="0" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="O23" s="0" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D24" s="0">
         <v>2</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>151</v>
+        <v>19</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>152</v>
+        <v>19</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="J24" s="0" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="K24" s="0" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="L24" s="0" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="M24" s="0" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="N24" s="0" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="O24" s="0" t="s">
-        <v>156</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25">
@@ -2496,13 +2526,13 @@
         <v>19</v>
       </c>
       <c r="D25" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="G25" s="0" t="s">
         <v>19</v>
@@ -2511,853 +2541,853 @@
         <v>19</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="J25" s="0" t="s">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="K25" s="0" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="L25" s="0" t="s">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="M25" s="0" t="s">
-        <v>24</v>
+        <v>134</v>
       </c>
       <c r="N25" s="0" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
       <c r="O25" s="0" t="s">
-        <v>162</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>119</v>
+        <v>19</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>121</v>
+        <v>19</v>
       </c>
       <c r="D26" s="0">
         <v>2</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>163</v>
+        <v>19</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>164</v>
+        <v>19</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="J26" s="0" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="K26" s="0" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="L26" s="0" t="s">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="M26" s="0" t="s">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="N26" s="0" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="O26" s="0" t="s">
-        <v>168</v>
+        <v>141</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>141</v>
+        <v>19</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>169</v>
+        <v>19</v>
       </c>
       <c r="C27" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="0">
+        <v>3</v>
+      </c>
+      <c r="E27" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="F27" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="I27" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="J27" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="K27" s="0" t="s">
         <v>143</v>
       </c>
-      <c r="D27" s="0">
-        <v>2</v>
-      </c>
-      <c r="E27" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="F27" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="G27" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="H27" s="0" t="s">
-        <v>171</v>
-      </c>
-      <c r="I27" s="0" t="s">
-        <v>88</v>
-      </c>
-      <c r="J27" s="0" t="s">
-        <v>172</v>
-      </c>
-      <c r="K27" s="0" t="s">
-        <v>173</v>
-      </c>
       <c r="L27" s="0" t="s">
-        <v>174</v>
+        <v>24</v>
       </c>
       <c r="M27" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="N27" s="0" t="s">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="O27" s="0" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D28" s="0">
         <v>2</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="G28" s="0" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="J28" s="0" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="K28" s="0" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="L28" s="0" t="s">
-        <v>35</v>
+        <v>134</v>
       </c>
       <c r="M28" s="0" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="N28" s="0" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="O28" s="0" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>169</v>
+        <v>19</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D29" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="G29" s="0" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="J29" s="0" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="K29" s="0" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="L29" s="0" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="M29" s="0" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="N29" s="0" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="O29" s="0" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>69</v>
+        <v>155</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="D30" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>55</v>
+        <v>157</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>55</v>
+        <v>157</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>185</v>
+        <v>158</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>158</v>
+        <v>101</v>
       </c>
       <c r="J30" s="0" t="s">
-        <v>187</v>
+        <v>160</v>
       </c>
       <c r="K30" s="0" t="s">
-        <v>188</v>
+        <v>161</v>
       </c>
       <c r="L30" s="0" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="M30" s="0" t="s">
         <v>19</v>
       </c>
       <c r="N30" s="0" t="s">
-        <v>189</v>
+        <v>162</v>
       </c>
       <c r="O30" s="0" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>69</v>
+        <v>155</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="D31" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>114</v>
+        <v>157</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>114</v>
+        <v>157</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="J31" s="0" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="K31" s="0" t="s">
-        <v>194</v>
+        <v>165</v>
       </c>
       <c r="L31" s="0" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="M31" s="0" t="s">
         <v>19</v>
       </c>
       <c r="N31" s="0" t="s">
-        <v>195</v>
+        <v>166</v>
       </c>
       <c r="O31" s="0" t="s">
-        <v>196</v>
+        <v>167</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>119</v>
+        <v>168</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="D32" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>55</v>
+        <v>171</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>55</v>
+        <v>171</v>
       </c>
       <c r="G32" s="0" t="s">
-        <v>122</v>
+        <v>172</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>123</v>
+        <v>173</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="J32" s="0" t="s">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="K32" s="0" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="L32" s="0" t="s">
-        <v>199</v>
+        <v>75</v>
       </c>
       <c r="M32" s="0" t="s">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="N32" s="0" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="O32" s="0" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>27</v>
+        <v>178</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>29</v>
+        <v>179</v>
       </c>
       <c r="D33" s="0">
         <v>2</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G33" s="0" t="s">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>71</v>
+        <v>181</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>158</v>
+        <v>63</v>
       </c>
       <c r="J33" s="0" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="K33" s="0" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="L33" s="0" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="M33" s="0" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="N33" s="0" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="O33" s="0" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="D34" s="0">
         <v>2</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G34" s="0" t="s">
-        <v>135</v>
+        <v>186</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>158</v>
+        <v>96</v>
       </c>
       <c r="J34" s="0" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="K34" s="0" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="L34" s="0" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M34" s="0" t="s">
         <v>19</v>
       </c>
       <c r="N34" s="0" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="O34" s="0" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>141</v>
+        <v>178</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="D35" s="0">
         <v>2</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="G35" s="0" t="s">
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>158</v>
+        <v>96</v>
       </c>
       <c r="J35" s="0" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="K35" s="0" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="L35" s="0" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="M35" s="0" t="s">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="N35" s="0" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="O35" s="0" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>27</v>
+        <v>178</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>29</v>
+        <v>179</v>
       </c>
       <c r="D36" s="0">
         <v>2</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G36" s="0" t="s">
-        <v>151</v>
+        <v>186</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>158</v>
+        <v>101</v>
       </c>
       <c r="J36" s="0" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="K36" s="0" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="L36" s="0" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="M36" s="0" t="s">
-        <v>174</v>
+        <v>19</v>
       </c>
       <c r="N36" s="0" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="O36" s="0" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>19</v>
+        <v>178</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>19</v>
+        <v>179</v>
       </c>
       <c r="D37" s="0">
         <v>2</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>157</v>
+        <v>90</v>
       </c>
       <c r="F37" s="0" t="s">
-        <v>157</v>
+        <v>90</v>
       </c>
       <c r="G37" s="0" t="s">
-        <v>19</v>
+        <v>180</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>218</v>
+        <v>101</v>
       </c>
       <c r="J37" s="0" t="s">
-        <v>219</v>
+        <v>200</v>
       </c>
       <c r="K37" s="0" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="L37" s="0" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="M37" s="0" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="N37" s="0" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="O37" s="0" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>119</v>
+        <v>178</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>121</v>
+        <v>179</v>
       </c>
       <c r="D38" s="0">
         <v>2</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="G38" s="0" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="J38" s="0" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="K38" s="0" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="L38" s="0" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="M38" s="0" t="s">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="N38" s="0" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="O38" s="0" t="s">
-        <v>226</v>
+        <v>207</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>141</v>
+        <v>208</v>
       </c>
       <c r="B39" s="0" t="s">
         <v>169</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>143</v>
+        <v>209</v>
       </c>
       <c r="D39" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>76</v>
+        <v>210</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>76</v>
+        <v>210</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>170</v>
+        <v>211</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>158</v>
+        <v>101</v>
       </c>
       <c r="J39" s="0" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="K39" s="0" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="L39" s="0" t="s">
-        <v>35</v>
+        <v>134</v>
       </c>
       <c r="M39" s="0" t="s">
-        <v>199</v>
+        <v>75</v>
       </c>
       <c r="N39" s="0" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="O39" s="0" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>27</v>
+        <v>217</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
       <c r="D40" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>31</v>
+        <v>219</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>32</v>
+        <v>220</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>218</v>
+        <v>131</v>
       </c>
       <c r="J40" s="0" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K40" s="0" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="L40" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="M40" s="0" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="N40" s="0" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="O40" s="0" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>27</v>
+        <v>225</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>169</v>
+        <v>226</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>29</v>
+        <v>227</v>
       </c>
       <c r="D41" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>82</v>
+        <v>228</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>82</v>
+        <v>228</v>
       </c>
       <c r="G41" s="0" t="s">
-        <v>45</v>
+        <v>229</v>
       </c>
       <c r="H41" s="0" t="s">
-        <v>46</v>
+        <v>230</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>218</v>
+        <v>101</v>
       </c>
       <c r="J41" s="0" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="K41" s="0" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="L41" s="0" t="s">
-        <v>237</v>
+        <v>134</v>
       </c>
       <c r="M41" s="0" t="s">
-        <v>35</v>
+        <v>139</v>
       </c>
       <c r="N41" s="0" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="O41" s="0" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>119</v>
+        <v>225</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>69</v>
+        <v>155</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>121</v>
+        <v>227</v>
       </c>
       <c r="D42" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>55</v>
+        <v>228</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>55</v>
+        <v>228</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="H42" s="0" t="s">
-        <v>186</v>
+        <v>220</v>
       </c>
       <c r="I42" s="0" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="J42" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="K42" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="L42" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="M42" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="N42" s="0" t="s">
+        <v>239</v>
+      </c>
+      <c r="O42" s="0" t="s">
         <v>240</v>
-      </c>
-      <c r="K42" s="0" t="s">
-        <v>241</v>
-      </c>
-      <c r="L42" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="M42" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="N42" s="0" t="s">
-        <v>242</v>
-      </c>
-      <c r="O42" s="0" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>133</v>
+        <v>225</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>69</v>
+        <v>241</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>134</v>
+        <v>227</v>
       </c>
       <c r="D43" s="0">
         <v>2</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>114</v>
+        <v>228</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>114</v>
+        <v>228</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>191</v>
+        <v>242</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>192</v>
+        <v>243</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="J43" s="0" t="s">
         <v>244</v>
@@ -3366,10 +3396,10 @@
         <v>245</v>
       </c>
       <c r="L43" s="0" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="M43" s="0" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="N43" s="0" t="s">
         <v>246</v>
@@ -3380,1488 +3410,1488 @@
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>19</v>
+        <v>248</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>19</v>
+        <v>249</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>19</v>
+        <v>250</v>
       </c>
       <c r="D44" s="0">
         <v>2</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>19</v>
+        <v>251</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>19</v>
+        <v>252</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>218</v>
+        <v>63</v>
       </c>
       <c r="J44" s="0" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="K44" s="0" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="L44" s="0" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="M44" s="0" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="N44" s="0" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="O44" s="0" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>119</v>
+        <v>248</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>120</v>
+        <v>241</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>121</v>
+        <v>250</v>
       </c>
       <c r="D45" s="0">
         <v>2</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>122</v>
+        <v>257</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>123</v>
+        <v>258</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>218</v>
+        <v>63</v>
       </c>
       <c r="J45" s="0" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="K45" s="0" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="L45" s="0" t="s">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="M45" s="0" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="N45" s="0" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="O45" s="0" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>19</v>
+        <v>248</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>19</v>
+        <v>249</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>19</v>
+        <v>250</v>
       </c>
       <c r="D46" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>19</v>
+        <v>251</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>19</v>
+        <v>252</v>
       </c>
       <c r="I46" s="0" t="s">
-        <v>218</v>
+        <v>96</v>
       </c>
       <c r="J46" s="0" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="K46" s="0" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="L46" s="0" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="M46" s="0" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="N46" s="0" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="O46" s="0" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>27</v>
+        <v>248</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>128</v>
+        <v>241</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>29</v>
+        <v>250</v>
       </c>
       <c r="D47" s="0">
         <v>2</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>70</v>
+        <v>257</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>71</v>
+        <v>258</v>
       </c>
       <c r="I47" s="0" t="s">
-        <v>218</v>
+        <v>96</v>
       </c>
       <c r="J47" s="0" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="K47" s="0" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="L47" s="0" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="M47" s="0" t="s">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="N47" s="0" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="O47" s="0" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>69</v>
+        <v>271</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="D48" s="0">
         <v>1</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>266</v>
+        <v>51</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>266</v>
+        <v>51</v>
       </c>
       <c r="G48" s="0" t="s">
-        <v>267</v>
+        <v>159</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="I48" s="0" t="s">
-        <v>218</v>
+        <v>101</v>
       </c>
       <c r="J48" s="0" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="K48" s="0" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="L48" s="0" t="s">
-        <v>41</v>
+        <v>134</v>
       </c>
       <c r="M48" s="0" t="s">
         <v>19</v>
       </c>
       <c r="N48" s="0" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="O48" s="0" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>19</v>
+        <v>248</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>19</v>
+        <v>249</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>19</v>
+        <v>250</v>
       </c>
       <c r="D49" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="F49" s="0" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="G49" s="0" t="s">
-        <v>19</v>
+        <v>251</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>19</v>
+        <v>252</v>
       </c>
       <c r="I49" s="0" t="s">
-        <v>218</v>
+        <v>101</v>
       </c>
       <c r="J49" s="0" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="K49" s="0" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="L49" s="0" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="M49" s="0" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="N49" s="0" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="O49" s="0" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>19</v>
+        <v>248</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>19</v>
+        <v>241</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>19</v>
+        <v>250</v>
       </c>
       <c r="D50" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="G50" s="0" t="s">
-        <v>19</v>
+        <v>257</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>19</v>
+        <v>258</v>
       </c>
       <c r="I50" s="0" t="s">
-        <v>218</v>
+        <v>101</v>
       </c>
       <c r="J50" s="0" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="K50" s="0" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="L50" s="0" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="M50" s="0" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="N50" s="0" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="O50" s="0" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>141</v>
+        <v>248</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>28</v>
+        <v>169</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>143</v>
+        <v>250</v>
       </c>
       <c r="D51" s="0">
         <v>1</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="G51" s="0" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>280</v>
+        <v>186</v>
       </c>
       <c r="I51" s="0" t="s">
-        <v>218</v>
+        <v>131</v>
       </c>
       <c r="J51" s="0" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="K51" s="0" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="L51" s="0" t="s">
-        <v>237</v>
+        <v>139</v>
       </c>
       <c r="M51" s="0" t="s">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="N51" s="0" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="O51" s="0" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>133</v>
+        <v>290</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>120</v>
+        <v>271</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>134</v>
+        <v>291</v>
       </c>
       <c r="D52" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>114</v>
+        <v>292</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>114</v>
+        <v>292</v>
       </c>
       <c r="G52" s="0" t="s">
-        <v>135</v>
+        <v>293</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>136</v>
+        <v>294</v>
       </c>
       <c r="I52" s="0" t="s">
-        <v>218</v>
+        <v>101</v>
       </c>
       <c r="J52" s="0" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="K52" s="0" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="L52" s="0" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="M52" s="0" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="N52" s="0" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="O52" s="0" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>19</v>
+        <v>290</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>19</v>
+        <v>155</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>19</v>
+        <v>291</v>
       </c>
       <c r="D53" s="0">
         <v>1</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>19</v>
+        <v>292</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>19</v>
+        <v>292</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>19</v>
+        <v>299</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>19</v>
+        <v>300</v>
       </c>
       <c r="I53" s="0" t="s">
-        <v>218</v>
+        <v>131</v>
       </c>
       <c r="J53" s="0" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="K53" s="0" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="L53" s="0" t="s">
         <v>19</v>
       </c>
       <c r="M53" s="0" t="s">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="N53" s="0" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="O53" s="0" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
-        <v>141</v>
+        <v>290</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>143</v>
+        <v>291</v>
       </c>
       <c r="D54" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>76</v>
+        <v>292</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>76</v>
+        <v>292</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>144</v>
+        <v>305</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>145</v>
+        <v>306</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>218</v>
+        <v>131</v>
       </c>
       <c r="J54" s="0" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="K54" s="0" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="L54" s="0" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="M54" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="N54" s="0" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="O54" s="0" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>44</v>
+        <v>271</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="D55" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>218</v>
+        <v>21</v>
       </c>
       <c r="J55" s="0" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="K55" s="0" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="L55" s="0" t="s">
-        <v>237</v>
+        <v>75</v>
       </c>
       <c r="M55" s="0" t="s">
-        <v>199</v>
+        <v>24</v>
       </c>
       <c r="N55" s="0" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="O55" s="0" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="s">
-        <v>27</v>
+        <v>311</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>150</v>
+        <v>226</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>29</v>
+        <v>312</v>
       </c>
       <c r="D56" s="0">
         <v>2</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>151</v>
+        <v>320</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>152</v>
+        <v>321</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>218</v>
+        <v>21</v>
       </c>
       <c r="J56" s="0" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="K56" s="0" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
       <c r="L56" s="0" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="M56" s="0" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="N56" s="0" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="O56" s="0" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>28</v>
+        <v>155</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D57" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>218</v>
+        <v>27</v>
       </c>
       <c r="J57" s="0" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="K57" s="0" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="L57" s="0" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="M57" s="0" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="N57" s="0" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="O57" s="0" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="s">
-        <v>19</v>
+        <v>311</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>19</v>
+        <v>332</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>19</v>
+        <v>312</v>
       </c>
       <c r="D58" s="0">
         <v>2</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>157</v>
+        <v>57</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>157</v>
+        <v>57</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>19</v>
+        <v>326</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>19</v>
+        <v>327</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>319</v>
+        <v>63</v>
       </c>
       <c r="J58" s="0" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="K58" s="0" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="L58" s="0" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="M58" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="N58" s="0" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="O58" s="0" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>120</v>
+        <v>337</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="D59" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>326</v>
+        <v>57</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>326</v>
+        <v>57</v>
       </c>
       <c r="G59" s="0" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="H59" s="0" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="I59" s="0" t="s">
-        <v>218</v>
+        <v>63</v>
       </c>
       <c r="J59" s="0" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="K59" s="0" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="L59" s="0" t="s">
-        <v>237</v>
+        <v>30</v>
       </c>
       <c r="M59" s="0" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="N59" s="0" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="O59" s="0" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="s">
-        <v>119</v>
+        <v>311</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>142</v>
+        <v>249</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>121</v>
+        <v>312</v>
       </c>
       <c r="D60" s="0">
         <v>2</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>163</v>
+        <v>314</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>164</v>
+        <v>315</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>218</v>
+        <v>96</v>
       </c>
       <c r="J60" s="0" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="K60" s="0" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="L60" s="0" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="M60" s="0" t="s">
         <v>24</v>
       </c>
       <c r="N60" s="0" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="O60" s="0" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="s">
-        <v>141</v>
+        <v>311</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>169</v>
+        <v>241</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>143</v>
+        <v>312</v>
       </c>
       <c r="D61" s="0">
         <v>2</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>170</v>
+        <v>320</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>171</v>
+        <v>321</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>218</v>
+        <v>96</v>
       </c>
       <c r="J61" s="0" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="K61" s="0" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="L61" s="0" t="s">
         <v>24</v>
       </c>
       <c r="M61" s="0" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="N61" s="0" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="O61" s="0" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="s">
-        <v>19</v>
+        <v>311</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>19</v>
+        <v>332</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>19</v>
+        <v>312</v>
       </c>
       <c r="D62" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>19</v>
+        <v>326</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>19</v>
+        <v>327</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>341</v>
+        <v>96</v>
       </c>
       <c r="J62" s="0" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="K62" s="0" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="L62" s="0" t="s">
-        <v>237</v>
+        <v>60</v>
       </c>
       <c r="M62" s="0" t="s">
-        <v>237</v>
+        <v>30</v>
       </c>
       <c r="N62" s="0" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="O62" s="0" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="s">
-        <v>19</v>
+        <v>311</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>19</v>
+        <v>337</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>19</v>
+        <v>312</v>
       </c>
       <c r="D63" s="0">
         <v>2</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="F63" s="0" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="G63" s="0" t="s">
-        <v>19</v>
+        <v>338</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>19</v>
+        <v>339</v>
       </c>
       <c r="I63" s="0" t="s">
-        <v>341</v>
+        <v>96</v>
       </c>
       <c r="J63" s="0" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="K63" s="0" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="L63" s="0" t="s">
-        <v>199</v>
+        <v>30</v>
       </c>
       <c r="M63" s="0" t="s">
-        <v>19</v>
+        <v>238</v>
       </c>
       <c r="N63" s="0" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="O63" s="0" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>69</v>
+        <v>249</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D64" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>312</v>
+        <v>57</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>312</v>
+        <v>57</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>350</v>
+        <v>314</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>351</v>
+        <v>315</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>341</v>
+        <v>101</v>
       </c>
       <c r="J64" s="0" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="K64" s="0" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="L64" s="0" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="M64" s="0" t="s">
-        <v>199</v>
+        <v>24</v>
       </c>
       <c r="N64" s="0" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="O64" s="0" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="s">
-        <v>27</v>
+        <v>311</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>169</v>
+        <v>241</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>29</v>
+        <v>312</v>
       </c>
       <c r="D65" s="0">
         <v>2</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="G65" s="0" t="s">
-        <v>45</v>
+        <v>320</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>46</v>
+        <v>321</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>341</v>
+        <v>101</v>
       </c>
       <c r="J65" s="0" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="K65" s="0" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="L65" s="0" t="s">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="M65" s="0" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="N65" s="0" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="O65" s="0" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="s">
-        <v>19</v>
+        <v>311</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>19</v>
+        <v>332</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>19</v>
+        <v>312</v>
       </c>
       <c r="D66" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="G66" s="0" t="s">
-        <v>19</v>
+        <v>326</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>19</v>
+        <v>327</v>
       </c>
       <c r="I66" s="0" t="s">
-        <v>341</v>
+        <v>101</v>
       </c>
       <c r="J66" s="0" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="K66" s="0" t="s">
-        <v>361</v>
+        <v>115</v>
       </c>
       <c r="L66" s="0" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="M66" s="0" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="N66" s="0" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="O66" s="0" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="s">
-        <v>364</v>
+        <v>311</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>120</v>
+        <v>337</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>365</v>
+        <v>312</v>
       </c>
       <c r="D67" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>366</v>
+        <v>57</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>366</v>
+        <v>57</v>
       </c>
       <c r="G67" s="0" t="s">
-        <v>367</v>
+        <v>338</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>185</v>
+        <v>339</v>
       </c>
       <c r="I67" s="0" t="s">
-        <v>341</v>
+        <v>101</v>
       </c>
       <c r="J67" s="0" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="K67" s="0" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L67" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="M67" s="0" t="s">
-        <v>237</v>
+        <v>19</v>
       </c>
       <c r="N67" s="0" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="O67" s="0" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="s">
-        <v>119</v>
+        <v>311</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>69</v>
+        <v>241</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>121</v>
+        <v>312</v>
       </c>
       <c r="D68" s="0">
         <v>2</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G68" s="0" t="s">
-        <v>185</v>
+        <v>320</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>186</v>
+        <v>321</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>341</v>
+        <v>131</v>
       </c>
       <c r="J68" s="0" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="K68" s="0" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="L68" s="0" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="M68" s="0" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="N68" s="0" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="O68" s="0" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0" t="s">
-        <v>19</v>
+        <v>379</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>19</v>
+        <v>380</v>
       </c>
       <c r="D69" s="0">
         <v>2</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G69" s="0" t="s">
-        <v>19</v>
+        <v>306</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>19</v>
+        <v>381</v>
       </c>
       <c r="I69" s="0" t="s">
-        <v>341</v>
+        <v>63</v>
       </c>
       <c r="J69" s="0" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="K69" s="0" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="L69" s="0" t="s">
-        <v>237</v>
+        <v>48</v>
       </c>
       <c r="M69" s="0" t="s">
         <v>19</v>
       </c>
       <c r="N69" s="0" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="O69" s="0" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0" t="s">
-        <v>141</v>
+        <v>379</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>120</v>
+        <v>249</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>143</v>
+        <v>380</v>
       </c>
       <c r="D70" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>191</v>
+        <v>387</v>
       </c>
       <c r="I70" s="0" t="s">
-        <v>341</v>
+        <v>63</v>
       </c>
       <c r="J70" s="0" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="K70" s="0" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="L70" s="0" t="s">
-        <v>199</v>
+        <v>19</v>
       </c>
       <c r="M70" s="0" t="s">
-        <v>199</v>
+        <v>66</v>
       </c>
       <c r="N70" s="0" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="O70" s="0" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0" t="s">
-        <v>133</v>
+        <v>379</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>69</v>
+        <v>155</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>134</v>
+        <v>380</v>
       </c>
       <c r="D71" s="0">
         <v>2</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>192</v>
+        <v>392</v>
       </c>
       <c r="I71" s="0" t="s">
-        <v>341</v>
+        <v>96</v>
       </c>
       <c r="J71" s="0" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="K71" s="0" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="L71" s="0" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="M71" s="0" t="s">
         <v>19</v>
       </c>
       <c r="N71" s="0" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="O71" s="0" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0" t="s">
-        <v>297</v>
+        <v>379</v>
       </c>
       <c r="B72" s="0" t="s">
         <v>169</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>298</v>
+        <v>380</v>
       </c>
       <c r="D72" s="0">
         <v>2</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>299</v>
+        <v>37</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>299</v>
+        <v>37</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>389</v>
+        <v>306</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="I72" s="0" t="s">
-        <v>391</v>
+        <v>96</v>
       </c>
       <c r="J72" s="0" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="K72" s="0" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="L72" s="0" t="s">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="M72" s="0" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="N72" s="0" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="O72" s="0" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="s">
-        <v>297</v>
+        <v>379</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>69</v>
+        <v>249</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>298</v>
+        <v>380</v>
       </c>
       <c r="D73" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>299</v>
+        <v>37</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>299</v>
+        <v>37</v>
       </c>
       <c r="G73" s="0" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>391</v>
+        <v>96</v>
       </c>
       <c r="J73" s="0" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="K73" s="0" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="L73" s="0" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="M73" s="0" t="s">
-        <v>174</v>
+        <v>66</v>
       </c>
       <c r="N73" s="0" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="O73" s="0" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="s">
-        <v>402</v>
+        <v>379</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>69</v>
+        <v>155</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>403</v>
+        <v>380</v>
       </c>
       <c r="D74" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>157</v>
+        <v>37</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>157</v>
+        <v>37</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>396</v>
+        <v>173</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>341</v>
+        <v>101</v>
       </c>
       <c r="J74" s="0" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K74" s="0" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L74" s="0" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="M74" s="0" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="N74" s="0" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O74" s="0" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="s">
-        <v>310</v>
+        <v>379</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>311</v>
+        <v>380</v>
       </c>
       <c r="D75" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>312</v>
+        <v>37</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>312</v>
+        <v>37</v>
       </c>
       <c r="G75" s="0" t="s">
-        <v>408</v>
+        <v>306</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>122</v>
+        <v>381</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>341</v>
+        <v>101</v>
       </c>
       <c r="J75" s="0" t="s">
         <v>409</v>
@@ -4870,10 +4900,10 @@
         <v>410</v>
       </c>
       <c r="L75" s="0" t="s">
-        <v>41</v>
+        <v>238</v>
       </c>
       <c r="M75" s="0" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="N75" s="0" t="s">
         <v>411</v>
@@ -4884,31 +4914,31 @@
     </row>
     <row r="76">
       <c r="A76" s="0" t="s">
-        <v>19</v>
+        <v>379</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>19</v>
+        <v>249</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>19</v>
+        <v>380</v>
       </c>
       <c r="D76" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E76" s="0" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>19</v>
+        <v>386</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>19</v>
+        <v>387</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>341</v>
+        <v>101</v>
       </c>
       <c r="J76" s="0" t="s">
         <v>413</v>
@@ -4917,10 +4947,10 @@
         <v>414</v>
       </c>
       <c r="L76" s="0" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="M76" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="N76" s="0" t="s">
         <v>415</v>
@@ -4931,31 +4961,31 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="s">
-        <v>119</v>
+        <v>379</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>121</v>
+        <v>380</v>
       </c>
       <c r="D77" s="0">
         <v>2</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>122</v>
+        <v>173</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>123</v>
+        <v>392</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>341</v>
+        <v>131</v>
       </c>
       <c r="J77" s="0" t="s">
         <v>417</v>
@@ -4964,16 +4994,110 @@
         <v>418</v>
       </c>
       <c r="L77" s="0" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="M77" s="0" t="s">
-        <v>237</v>
+        <v>54</v>
       </c>
       <c r="N77" s="0" t="s">
         <v>419</v>
       </c>
       <c r="O77" s="0" t="s">
         <v>420</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="0" t="s">
+        <v>379</v>
+      </c>
+      <c r="B78" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="C78" s="0" t="s">
+        <v>380</v>
+      </c>
+      <c r="D78" s="0">
+        <v>2</v>
+      </c>
+      <c r="E78" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="F78" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="G78" s="0" t="s">
+        <v>306</v>
+      </c>
+      <c r="H78" s="0" t="s">
+        <v>381</v>
+      </c>
+      <c r="I78" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="J78" s="0" t="s">
+        <v>421</v>
+      </c>
+      <c r="K78" s="0" t="s">
+        <v>422</v>
+      </c>
+      <c r="L78" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="M78" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="N78" s="0" t="s">
+        <v>423</v>
+      </c>
+      <c r="O78" s="0" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="0" t="s">
+        <v>379</v>
+      </c>
+      <c r="B79" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="C79" s="0" t="s">
+        <v>380</v>
+      </c>
+      <c r="D79" s="0">
+        <v>2</v>
+      </c>
+      <c r="E79" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="F79" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="G79" s="0" t="s">
+        <v>425</v>
+      </c>
+      <c r="H79" s="0" t="s">
+        <v>426</v>
+      </c>
+      <c r="I79" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="J79" s="0" t="s">
+        <v>427</v>
+      </c>
+      <c r="K79" s="0" t="s">
+        <v>428</v>
+      </c>
+      <c r="L79" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="M79" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="N79" s="0" t="s">
+        <v>429</v>
+      </c>
+      <c r="O79" s="0" t="s">
+        <v>430</v>
       </c>
     </row>
   </sheetData>

--- a/荷量実績_20241014-20241021.xlsx
+++ b/荷量実績_20241014-20241021.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="443">
   <si>
     <t>項目名</t>
   </si>
@@ -481,6 +481,30 @@
     <t>\\192.168.1.166\share\iot\SyncBace\3\img\2024-10-21\61-70%\image_2024-10-21_13z52z20.jpg</t>
   </si>
   <si>
+    <t>2024/10/21 16:53</t>
+  </si>
+  <si>
+    <t>2024/10/21 16:56</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\3\img\2024-10-21\51-60%\image_2024-10-21_16z53z38.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\3\img\2024-10-21\31-40%\image_2024-10-21_16z55z59.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/21 17:01</t>
+  </si>
+  <si>
+    <t>2024/10/21 17:16</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\3\img\2024-10-21\11-20%\image_2024-10-21_17z01z14.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\3\img\2024-10-21\1-10%\image_2024-10-21_17z16z47.jpg</t>
+  </si>
+  <si>
     <t>8t常傭便1</t>
   </si>
   <si>
@@ -1154,6 +1178,18 @@
   </si>
   <si>
     <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-21\opening\image_2024-10-21_07z41z44.jpg</t>
+  </si>
+  <si>
+    <t>2024/10/21 16:51</t>
+  </si>
+  <si>
+    <t>2024/10/21 17:13</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-21\51-60%\image_2024-10-21_16z51z27.jpg</t>
+  </si>
+  <si>
+    <t>\\192.168.1.166\share\iot\SyncBace\2\img\2024-10-21\51-60%\image_2024-10-21_17z13z14.jpg</t>
   </si>
   <si>
     <t>豊鉄大型常傭便3</t>
@@ -1384,7 +1420,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:O79"/>
+  <dimension ref="A1:O82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2752,248 +2788,248 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="0">
+        <v>3</v>
+      </c>
+      <c r="E30" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="I30" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="J30" s="0" t="s">
         <v>154</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="K30" s="0" t="s">
         <v>155</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="L30" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="M30" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="N30" s="0" t="s">
         <v>156</v>
       </c>
-      <c r="D30" s="0">
-        <v>1</v>
-      </c>
-      <c r="E30" s="0" t="s">
+      <c r="O30" s="0" t="s">
         <v>157</v>
-      </c>
-      <c r="F30" s="0" t="s">
-        <v>157</v>
-      </c>
-      <c r="G30" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="H30" s="0" t="s">
-        <v>159</v>
-      </c>
-      <c r="I30" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="J30" s="0" t="s">
-        <v>160</v>
-      </c>
-      <c r="K30" s="0" t="s">
-        <v>161</v>
-      </c>
-      <c r="L30" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="M30" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="N30" s="0" t="s">
-        <v>162</v>
-      </c>
-      <c r="O30" s="0" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>154</v>
+        <v>19</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>156</v>
+        <v>19</v>
       </c>
       <c r="D31" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>158</v>
+        <v>19</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>159</v>
+        <v>19</v>
       </c>
       <c r="I31" s="0" t="s">
         <v>131</v>
       </c>
       <c r="J31" s="0" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="K31" s="0" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="L31" s="0" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="M31" s="0" t="s">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="N31" s="0" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="O31" s="0" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D32" s="0">
         <v>1</v>
       </c>
       <c r="E32" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="F32" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="G32" s="0" t="s">
+        <v>166</v>
+      </c>
+      <c r="H32" s="0" t="s">
+        <v>167</v>
+      </c>
+      <c r="I32" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="J32" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="K32" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="L32" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="M32" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="N32" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="O32" s="0" t="s">
         <v>171</v>
-      </c>
-      <c r="F32" s="0" t="s">
-        <v>171</v>
-      </c>
-      <c r="G32" s="0" t="s">
-        <v>172</v>
-      </c>
-      <c r="H32" s="0" t="s">
-        <v>173</v>
-      </c>
-      <c r="I32" s="0" t="s">
-        <v>131</v>
-      </c>
-      <c r="J32" s="0" t="s">
-        <v>174</v>
-      </c>
-      <c r="K32" s="0" t="s">
-        <v>175</v>
-      </c>
-      <c r="L32" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="M32" s="0" t="s">
-        <v>134</v>
-      </c>
-      <c r="N32" s="0" t="s">
-        <v>176</v>
-      </c>
-      <c r="O32" s="0" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="D33" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>90</v>
+        <v>165</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>90</v>
+        <v>165</v>
       </c>
       <c r="G33" s="0" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>63</v>
+        <v>131</v>
       </c>
       <c r="J33" s="0" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="K33" s="0" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="L33" s="0" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="M33" s="0" t="s">
         <v>19</v>
       </c>
       <c r="N33" s="0" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="O33" s="0" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
+        <v>176</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>177</v>
+      </c>
+      <c r="C34" s="0" t="s">
         <v>178</v>
       </c>
-      <c r="B34" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="C34" s="0" t="s">
+      <c r="D34" s="0">
+        <v>1</v>
+      </c>
+      <c r="E34" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="D34" s="0">
-        <v>2</v>
-      </c>
-      <c r="E34" s="0" t="s">
-        <v>90</v>
-      </c>
       <c r="F34" s="0" t="s">
-        <v>90</v>
+        <v>179</v>
       </c>
       <c r="G34" s="0" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="H34" s="0" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="J34" s="0" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="K34" s="0" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="L34" s="0" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="M34" s="0" t="s">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="N34" s="0" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="O34" s="0" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D35" s="0">
         <v>2</v>
@@ -3005,42 +3041,42 @@
         <v>90</v>
       </c>
       <c r="G35" s="0" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="J35" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="K35" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="L35" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="M35" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="N35" s="0" t="s">
         <v>192</v>
       </c>
-      <c r="K35" s="0" t="s">
+      <c r="O35" s="0" t="s">
         <v>193</v>
-      </c>
-      <c r="L35" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="M35" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="N35" s="0" t="s">
-        <v>194</v>
-      </c>
-      <c r="O35" s="0" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D36" s="0">
         <v>2</v>
@@ -3052,13 +3088,13 @@
         <v>90</v>
       </c>
       <c r="G36" s="0" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="H36" s="0" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="J36" s="0" t="s">
         <v>196</v>
@@ -3067,7 +3103,7 @@
         <v>197</v>
       </c>
       <c r="L36" s="0" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="M36" s="0" t="s">
         <v>19</v>
@@ -3081,13 +3117,13 @@
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D37" s="0">
         <v>2</v>
@@ -3099,13 +3135,13 @@
         <v>90</v>
       </c>
       <c r="G37" s="0" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="J37" s="0" t="s">
         <v>200</v>
@@ -3114,7 +3150,7 @@
         <v>201</v>
       </c>
       <c r="L37" s="0" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="M37" s="0" t="s">
         <v>19</v>
@@ -3128,13 +3164,13 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D38" s="0">
         <v>2</v>
@@ -3146,13 +3182,13 @@
         <v>90</v>
       </c>
       <c r="G38" s="0" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="H38" s="0" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="J38" s="0" t="s">
         <v>204</v>
@@ -3161,7 +3197,7 @@
         <v>205</v>
       </c>
       <c r="L38" s="0" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="M38" s="0" t="s">
         <v>19</v>
@@ -3175,143 +3211,143 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="D39" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>210</v>
+        <v>90</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>210</v>
+        <v>90</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>211</v>
+        <v>188</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="I39" s="0" t="s">
         <v>101</v>
       </c>
       <c r="J39" s="0" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="K39" s="0" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="L39" s="0" t="s">
-        <v>134</v>
+        <v>66</v>
       </c>
       <c r="M39" s="0" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="N39" s="0" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="O39" s="0" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>217</v>
+        <v>186</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>218</v>
+        <v>187</v>
       </c>
       <c r="D40" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>219</v>
+        <v>194</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="I40" s="0" t="s">
         <v>131</v>
       </c>
       <c r="J40" s="0" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="K40" s="0" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="L40" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="M40" s="0" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="N40" s="0" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="O40" s="0" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>226</v>
+        <v>177</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="D41" s="0">
         <v>1</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="G41" s="0" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="H41" s="0" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="I41" s="0" t="s">
         <v>101</v>
       </c>
       <c r="J41" s="0" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="K41" s="0" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="L41" s="0" t="s">
         <v>134</v>
       </c>
       <c r="M41" s="0" t="s">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="N41" s="0" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="O41" s="0" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
     </row>
     <row r="42">
@@ -3319,198 +3355,198 @@
         <v>225</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="C42" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="D42" s="0">
+        <v>3</v>
+      </c>
+      <c r="E42" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="F42" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="G42" s="0" t="s">
         <v>227</v>
       </c>
-      <c r="D42" s="0">
-        <v>1</v>
-      </c>
-      <c r="E42" s="0" t="s">
+      <c r="H42" s="0" t="s">
         <v>228</v>
       </c>
-      <c r="F42" s="0" t="s">
-        <v>228</v>
-      </c>
-      <c r="G42" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="H42" s="0" t="s">
-        <v>220</v>
-      </c>
       <c r="I42" s="0" t="s">
-        <v>235</v>
+        <v>131</v>
       </c>
       <c r="J42" s="0" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="K42" s="0" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="L42" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="M42" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="M42" s="0" t="s">
-        <v>238</v>
-      </c>
       <c r="N42" s="0" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="O42" s="0" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B43" s="0" t="s">
+        <v>234</v>
+      </c>
+      <c r="C43" s="0" t="s">
+        <v>235</v>
+      </c>
+      <c r="D43" s="0">
+        <v>1</v>
+      </c>
+      <c r="E43" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="F43" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="G43" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="H43" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="I43" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="J43" s="0" t="s">
+        <v>239</v>
+      </c>
+      <c r="K43" s="0" t="s">
+        <v>240</v>
+      </c>
+      <c r="L43" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="M43" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="N43" s="0" t="s">
         <v>241</v>
       </c>
-      <c r="C43" s="0" t="s">
-        <v>227</v>
-      </c>
-      <c r="D43" s="0">
-        <v>2</v>
-      </c>
-      <c r="E43" s="0" t="s">
-        <v>228</v>
-      </c>
-      <c r="F43" s="0" t="s">
-        <v>228</v>
-      </c>
-      <c r="G43" s="0" t="s">
+      <c r="O43" s="0" t="s">
         <v>242</v>
-      </c>
-      <c r="H43" s="0" t="s">
-        <v>243</v>
-      </c>
-      <c r="I43" s="0" t="s">
-        <v>235</v>
-      </c>
-      <c r="J43" s="0" t="s">
-        <v>244</v>
-      </c>
-      <c r="K43" s="0" t="s">
-        <v>245</v>
-      </c>
-      <c r="L43" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="M43" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="N43" s="0" t="s">
-        <v>246</v>
-      </c>
-      <c r="O43" s="0" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>249</v>
+        <v>163</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="D44" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>51</v>
+        <v>236</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>51</v>
+        <v>236</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>251</v>
+        <v>227</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>63</v>
+        <v>243</v>
       </c>
       <c r="J44" s="0" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="K44" s="0" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="L44" s="0" t="s">
         <v>54</v>
       </c>
       <c r="M44" s="0" t="s">
-        <v>66</v>
+        <v>246</v>
       </c>
       <c r="N44" s="0" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="O44" s="0" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="C45" s="0" t="s">
+        <v>235</v>
+      </c>
+      <c r="D45" s="0">
+        <v>2</v>
+      </c>
+      <c r="E45" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="F45" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="G45" s="0" t="s">
         <v>250</v>
       </c>
-      <c r="D45" s="0">
-        <v>2</v>
-      </c>
-      <c r="E45" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="F45" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="G45" s="0" t="s">
-        <v>257</v>
-      </c>
       <c r="H45" s="0" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>63</v>
+        <v>243</v>
       </c>
       <c r="J45" s="0" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="K45" s="0" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="L45" s="0" t="s">
-        <v>238</v>
+        <v>60</v>
       </c>
       <c r="M45" s="0" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="N45" s="0" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="O45" s="0" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="D46" s="0">
         <v>2</v>
@@ -3522,19 +3558,19 @@
         <v>51</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="I46" s="0" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="J46" s="0" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="K46" s="0" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L46" s="0" t="s">
         <v>54</v>
@@ -3543,21 +3579,21 @@
         <v>66</v>
       </c>
       <c r="N46" s="0" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="O46" s="0" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="D47" s="0">
         <v>2</v>
@@ -3569,13 +3605,13 @@
         <v>51</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="H47" s="0" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="I47" s="0" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="J47" s="0" t="s">
         <v>267</v>
@@ -3584,10 +3620,10 @@
         <v>268</v>
       </c>
       <c r="L47" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="M47" s="0" t="s">
         <v>75</v>
-      </c>
-      <c r="M47" s="0" t="s">
-        <v>139</v>
       </c>
       <c r="N47" s="0" t="s">
         <v>269</v>
@@ -3598,16 +3634,16 @@
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="D48" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48" s="0" t="s">
         <v>51</v>
@@ -3616,42 +3652,42 @@
         <v>51</v>
       </c>
       <c r="G48" s="0" t="s">
-        <v>159</v>
+        <v>259</v>
       </c>
       <c r="H48" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="I48" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="J48" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="K48" s="0" t="s">
         <v>272</v>
       </c>
-      <c r="I48" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="J48" s="0" t="s">
+      <c r="L48" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="M48" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="N48" s="0" t="s">
         <v>273</v>
       </c>
-      <c r="K48" s="0" t="s">
+      <c r="O48" s="0" t="s">
         <v>274</v>
-      </c>
-      <c r="L48" s="0" t="s">
-        <v>134</v>
-      </c>
-      <c r="M48" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="N48" s="0" t="s">
-        <v>275</v>
-      </c>
-      <c r="O48" s="0" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B49" s="0" t="s">
         <v>249</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="D49" s="0">
         <v>2</v>
@@ -3663,45 +3699,45 @@
         <v>51</v>
       </c>
       <c r="G49" s="0" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="H49" s="0" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="I49" s="0" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="J49" s="0" t="s">
+        <v>275</v>
+      </c>
+      <c r="K49" s="0" t="s">
+        <v>276</v>
+      </c>
+      <c r="L49" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="M49" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="N49" s="0" t="s">
         <v>277</v>
       </c>
-      <c r="K49" s="0" t="s">
+      <c r="O49" s="0" t="s">
         <v>278</v>
-      </c>
-      <c r="L49" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="M49" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="N49" s="0" t="s">
-        <v>279</v>
-      </c>
-      <c r="O49" s="0" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>241</v>
+        <v>279</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="D50" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50" s="0" t="s">
         <v>51</v>
@@ -3710,10 +3746,10 @@
         <v>51</v>
       </c>
       <c r="G50" s="0" t="s">
-        <v>257</v>
+        <v>167</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="I50" s="0" t="s">
         <v>101</v>
@@ -3725,10 +3761,10 @@
         <v>282</v>
       </c>
       <c r="L50" s="0" t="s">
-        <v>24</v>
+        <v>134</v>
       </c>
       <c r="M50" s="0" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="N50" s="0" t="s">
         <v>283</v>
@@ -3739,16 +3775,16 @@
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>169</v>
+        <v>257</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="D51" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" s="0" t="s">
         <v>51</v>
@@ -3757,348 +3793,348 @@
         <v>51</v>
       </c>
       <c r="G51" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="H51" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="I51" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="J51" s="0" t="s">
         <v>285</v>
       </c>
-      <c r="H51" s="0" t="s">
-        <v>186</v>
-      </c>
-      <c r="I51" s="0" t="s">
-        <v>131</v>
-      </c>
-      <c r="J51" s="0" t="s">
+      <c r="K51" s="0" t="s">
         <v>286</v>
       </c>
-      <c r="K51" s="0" t="s">
+      <c r="L51" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="M51" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="N51" s="0" t="s">
         <v>287</v>
       </c>
-      <c r="L51" s="0" t="s">
-        <v>139</v>
-      </c>
-      <c r="M51" s="0" t="s">
-        <v>139</v>
-      </c>
-      <c r="N51" s="0" t="s">
+      <c r="O51" s="0" t="s">
         <v>288</v>
-      </c>
-      <c r="O51" s="0" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>271</v>
+        <v>249</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>291</v>
+        <v>258</v>
       </c>
       <c r="D52" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>292</v>
+        <v>51</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>292</v>
+        <v>51</v>
       </c>
       <c r="G52" s="0" t="s">
-        <v>293</v>
+        <v>265</v>
       </c>
       <c r="H52" s="0" t="s">
-        <v>294</v>
+        <v>266</v>
       </c>
       <c r="I52" s="0" t="s">
         <v>101</v>
       </c>
       <c r="J52" s="0" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="K52" s="0" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="L52" s="0" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="M52" s="0" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="N52" s="0" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="O52" s="0" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>291</v>
+        <v>258</v>
       </c>
       <c r="D53" s="0">
         <v>1</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>292</v>
+        <v>51</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>292</v>
+        <v>51</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>300</v>
+        <v>194</v>
       </c>
       <c r="I53" s="0" t="s">
         <v>131</v>
       </c>
       <c r="J53" s="0" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="K53" s="0" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="L53" s="0" t="s">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="M53" s="0" t="s">
         <v>139</v>
       </c>
       <c r="N53" s="0" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="O53" s="0" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>169</v>
+        <v>279</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="D54" s="0">
         <v>1</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="G54" s="0" t="s">
+        <v>301</v>
+      </c>
+      <c r="H54" s="0" t="s">
+        <v>302</v>
+      </c>
+      <c r="I54" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="J54" s="0" t="s">
+        <v>303</v>
+      </c>
+      <c r="K54" s="0" t="s">
+        <v>304</v>
+      </c>
+      <c r="L54" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="M54" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="N54" s="0" t="s">
         <v>305</v>
       </c>
-      <c r="H54" s="0" t="s">
+      <c r="O54" s="0" t="s">
         <v>306</v>
-      </c>
-      <c r="I54" s="0" t="s">
-        <v>131</v>
-      </c>
-      <c r="J54" s="0" t="s">
-        <v>307</v>
-      </c>
-      <c r="K54" s="0" t="s">
-        <v>308</v>
-      </c>
-      <c r="L54" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="M54" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="N54" s="0" t="s">
-        <v>309</v>
-      </c>
-      <c r="O54" s="0" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
+        <v>298</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>163</v>
+      </c>
+      <c r="C55" s="0" t="s">
+        <v>299</v>
+      </c>
+      <c r="D55" s="0">
+        <v>1</v>
+      </c>
+      <c r="E55" s="0" t="s">
+        <v>300</v>
+      </c>
+      <c r="F55" s="0" t="s">
+        <v>300</v>
+      </c>
+      <c r="G55" s="0" t="s">
+        <v>307</v>
+      </c>
+      <c r="H55" s="0" t="s">
+        <v>308</v>
+      </c>
+      <c r="I55" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="J55" s="0" t="s">
+        <v>309</v>
+      </c>
+      <c r="K55" s="0" t="s">
+        <v>310</v>
+      </c>
+      <c r="L55" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="M55" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="N55" s="0" t="s">
         <v>311</v>
       </c>
-      <c r="B55" s="0" t="s">
-        <v>271</v>
-      </c>
-      <c r="C55" s="0" t="s">
+      <c r="O55" s="0" t="s">
         <v>312</v>
-      </c>
-      <c r="D55" s="0">
-        <v>2</v>
-      </c>
-      <c r="E55" s="0" t="s">
-        <v>313</v>
-      </c>
-      <c r="F55" s="0" t="s">
-        <v>313</v>
-      </c>
-      <c r="G55" s="0" t="s">
-        <v>314</v>
-      </c>
-      <c r="H55" s="0" t="s">
-        <v>315</v>
-      </c>
-      <c r="I55" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="J55" s="0" t="s">
-        <v>316</v>
-      </c>
-      <c r="K55" s="0" t="s">
-        <v>317</v>
-      </c>
-      <c r="L55" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="M55" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="N55" s="0" t="s">
-        <v>318</v>
-      </c>
-      <c r="O55" s="0" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="s">
-        <v>311</v>
+        <v>298</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>226</v>
+        <v>177</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="D56" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56" s="0" t="s">
+        <v>300</v>
+      </c>
+      <c r="F56" s="0" t="s">
+        <v>300</v>
+      </c>
+      <c r="G56" s="0" t="s">
         <v>313</v>
       </c>
-      <c r="F56" s="0" t="s">
-        <v>313</v>
-      </c>
-      <c r="G56" s="0" t="s">
-        <v>320</v>
-      </c>
       <c r="H56" s="0" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="I56" s="0" t="s">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="J56" s="0" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="K56" s="0" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="L56" s="0" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="M56" s="0" t="s">
         <v>30</v>
       </c>
       <c r="N56" s="0" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="O56" s="0" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>155</v>
+        <v>279</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="D57" s="0">
         <v>2</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="G57" s="0" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H57" s="0" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="I57" s="0" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J57" s="0" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="K57" s="0" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="L57" s="0" t="s">
         <v>75</v>
       </c>
       <c r="M57" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="N57" s="0" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="O57" s="0" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>332</v>
+        <v>234</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="D58" s="0">
         <v>2</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>57</v>
+        <v>321</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>57</v>
+        <v>321</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H58" s="0" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="J58" s="0" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="K58" s="0" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="L58" s="0" t="s">
         <v>19</v>
@@ -4107,68 +4143,68 @@
         <v>30</v>
       </c>
       <c r="N58" s="0" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="O58" s="0" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B59" s="0" t="s">
+        <v>163</v>
+      </c>
+      <c r="C59" s="0" t="s">
+        <v>320</v>
+      </c>
+      <c r="D59" s="0">
+        <v>2</v>
+      </c>
+      <c r="E59" s="0" t="s">
+        <v>321</v>
+      </c>
+      <c r="F59" s="0" t="s">
+        <v>321</v>
+      </c>
+      <c r="G59" s="0" t="s">
+        <v>334</v>
+      </c>
+      <c r="H59" s="0" t="s">
+        <v>335</v>
+      </c>
+      <c r="I59" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="J59" s="0" t="s">
+        <v>336</v>
+      </c>
+      <c r="K59" s="0" t="s">
         <v>337</v>
       </c>
-      <c r="C59" s="0" t="s">
-        <v>312</v>
-      </c>
-      <c r="D59" s="0">
-        <v>2</v>
-      </c>
-      <c r="E59" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="F59" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="G59" s="0" t="s">
+      <c r="L59" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="M59" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="N59" s="0" t="s">
         <v>338</v>
       </c>
-      <c r="H59" s="0" t="s">
+      <c r="O59" s="0" t="s">
         <v>339</v>
-      </c>
-      <c r="I59" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="J59" s="0" t="s">
-        <v>340</v>
-      </c>
-      <c r="K59" s="0" t="s">
-        <v>341</v>
-      </c>
-      <c r="L59" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="M59" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="N59" s="0" t="s">
-        <v>342</v>
-      </c>
-      <c r="O59" s="0" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>249</v>
+        <v>340</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="D60" s="0">
         <v>2</v>
@@ -4180,42 +4216,42 @@
         <v>57</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="H60" s="0" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="J60" s="0" t="s">
+        <v>341</v>
+      </c>
+      <c r="K60" s="0" t="s">
+        <v>342</v>
+      </c>
+      <c r="L60" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="M60" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="N60" s="0" t="s">
+        <v>343</v>
+      </c>
+      <c r="O60" s="0" t="s">
         <v>344</v>
-      </c>
-      <c r="K60" s="0" t="s">
-        <v>345</v>
-      </c>
-      <c r="L60" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="M60" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="N60" s="0" t="s">
-        <v>346</v>
-      </c>
-      <c r="O60" s="0" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>241</v>
+        <v>345</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="D61" s="0">
         <v>2</v>
@@ -4227,13 +4263,13 @@
         <v>57</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>320</v>
+        <v>346</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>321</v>
+        <v>347</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="J61" s="0" t="s">
         <v>348</v>
@@ -4242,10 +4278,10 @@
         <v>349</v>
       </c>
       <c r="L61" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="M61" s="0" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="N61" s="0" t="s">
         <v>350</v>
@@ -4256,13 +4292,13 @@
     </row>
     <row r="62">
       <c r="A62" s="0" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>332</v>
+        <v>257</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="D62" s="0">
         <v>2</v>
@@ -4274,10 +4310,10 @@
         <v>57</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="I62" s="0" t="s">
         <v>96</v>
@@ -4289,10 +4325,10 @@
         <v>353</v>
       </c>
       <c r="L62" s="0" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="M62" s="0" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="N62" s="0" t="s">
         <v>354</v>
@@ -4303,13 +4339,13 @@
     </row>
     <row r="63">
       <c r="A63" s="0" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>337</v>
+        <v>249</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="D63" s="0">
         <v>2</v>
@@ -4321,10 +4357,10 @@
         <v>57</v>
       </c>
       <c r="G63" s="0" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="I63" s="0" t="s">
         <v>96</v>
@@ -4336,10 +4372,10 @@
         <v>357</v>
       </c>
       <c r="L63" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="M63" s="0" t="s">
         <v>30</v>
-      </c>
-      <c r="M63" s="0" t="s">
-        <v>238</v>
       </c>
       <c r="N63" s="0" t="s">
         <v>358</v>
@@ -4350,13 +4386,13 @@
     </row>
     <row r="64">
       <c r="A64" s="0" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>249</v>
+        <v>340</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="D64" s="0">
         <v>2</v>
@@ -4368,13 +4404,13 @@
         <v>57</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="H64" s="0" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="J64" s="0" t="s">
         <v>360</v>
@@ -4383,10 +4419,10 @@
         <v>361</v>
       </c>
       <c r="L64" s="0" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="M64" s="0" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="N64" s="0" t="s">
         <v>362</v>
@@ -4397,13 +4433,13 @@
     </row>
     <row r="65">
       <c r="A65" s="0" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>241</v>
+        <v>345</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="D65" s="0">
         <v>2</v>
@@ -4415,13 +4451,13 @@
         <v>57</v>
       </c>
       <c r="G65" s="0" t="s">
-        <v>320</v>
+        <v>346</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>321</v>
+        <v>347</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="J65" s="0" t="s">
         <v>364</v>
@@ -4430,10 +4466,10 @@
         <v>365</v>
       </c>
       <c r="L65" s="0" t="s">
-        <v>134</v>
+        <v>30</v>
       </c>
       <c r="M65" s="0" t="s">
-        <v>75</v>
+        <v>246</v>
       </c>
       <c r="N65" s="0" t="s">
         <v>366</v>
@@ -4444,13 +4480,13 @@
     </row>
     <row r="66">
       <c r="A66" s="0" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>332</v>
+        <v>257</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="D66" s="0">
         <v>2</v>
@@ -4462,10 +4498,10 @@
         <v>57</v>
       </c>
       <c r="G66" s="0" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="I66" s="0" t="s">
         <v>101</v>
@@ -4474,30 +4510,30 @@
         <v>368</v>
       </c>
       <c r="K66" s="0" t="s">
-        <v>115</v>
+        <v>369</v>
       </c>
       <c r="L66" s="0" t="s">
         <v>75</v>
       </c>
       <c r="M66" s="0" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="N66" s="0" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O66" s="0" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>337</v>
+        <v>249</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="D67" s="0">
         <v>2</v>
@@ -4509,42 +4545,42 @@
         <v>57</v>
       </c>
       <c r="G67" s="0" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="I67" s="0" t="s">
         <v>101</v>
       </c>
       <c r="J67" s="0" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K67" s="0" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L67" s="0" t="s">
-        <v>24</v>
+        <v>134</v>
       </c>
       <c r="M67" s="0" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="N67" s="0" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O67" s="0" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>241</v>
+        <v>340</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="D68" s="0">
         <v>2</v>
@@ -4556,25 +4592,25 @@
         <v>57</v>
       </c>
       <c r="G68" s="0" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="I68" s="0" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="J68" s="0" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K68" s="0" t="s">
-        <v>376</v>
+        <v>115</v>
       </c>
       <c r="L68" s="0" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="M68" s="0" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="N68" s="0" t="s">
         <v>377</v>
@@ -4585,154 +4621,154 @@
     </row>
     <row r="69">
       <c r="A69" s="0" t="s">
+        <v>319</v>
+      </c>
+      <c r="B69" s="0" t="s">
+        <v>345</v>
+      </c>
+      <c r="C69" s="0" t="s">
+        <v>320</v>
+      </c>
+      <c r="D69" s="0">
+        <v>2</v>
+      </c>
+      <c r="E69" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="F69" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="G69" s="0" t="s">
+        <v>346</v>
+      </c>
+      <c r="H69" s="0" t="s">
+        <v>347</v>
+      </c>
+      <c r="I69" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="J69" s="0" t="s">
         <v>379</v>
       </c>
-      <c r="B69" s="0" t="s">
-        <v>169</v>
-      </c>
-      <c r="C69" s="0" t="s">
+      <c r="K69" s="0" t="s">
         <v>380</v>
       </c>
-      <c r="D69" s="0">
-        <v>2</v>
-      </c>
-      <c r="E69" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="F69" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="G69" s="0" t="s">
-        <v>306</v>
-      </c>
-      <c r="H69" s="0" t="s">
+      <c r="L69" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="M69" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="N69" s="0" t="s">
         <v>381</v>
       </c>
-      <c r="I69" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="J69" s="0" t="s">
+      <c r="O69" s="0" t="s">
         <v>382</v>
-      </c>
-      <c r="K69" s="0" t="s">
-        <v>383</v>
-      </c>
-      <c r="L69" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="M69" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="N69" s="0" t="s">
-        <v>384</v>
-      </c>
-      <c r="O69" s="0" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0" t="s">
-        <v>379</v>
+        <v>319</v>
       </c>
       <c r="B70" s="0" t="s">
         <v>249</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>380</v>
+        <v>320</v>
       </c>
       <c r="D70" s="0">
         <v>2</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="G70" s="0" t="s">
+        <v>328</v>
+      </c>
+      <c r="H70" s="0" t="s">
+        <v>329</v>
+      </c>
+      <c r="I70" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="J70" s="0" t="s">
+        <v>383</v>
+      </c>
+      <c r="K70" s="0" t="s">
+        <v>384</v>
+      </c>
+      <c r="L70" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="M70" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="N70" s="0" t="s">
+        <v>385</v>
+      </c>
+      <c r="O70" s="0" t="s">
         <v>386</v>
-      </c>
-      <c r="H70" s="0" t="s">
-        <v>387</v>
-      </c>
-      <c r="I70" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="J70" s="0" t="s">
-        <v>388</v>
-      </c>
-      <c r="K70" s="0" t="s">
-        <v>389</v>
-      </c>
-      <c r="L70" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="M70" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="N70" s="0" t="s">
-        <v>390</v>
-      </c>
-      <c r="O70" s="0" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0" t="s">
-        <v>379</v>
+        <v>319</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>155</v>
+        <v>340</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>380</v>
+        <v>320</v>
       </c>
       <c r="D71" s="0">
         <v>2</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>173</v>
+        <v>334</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>392</v>
+        <v>335</v>
       </c>
       <c r="I71" s="0" t="s">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="J71" s="0" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="K71" s="0" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="L71" s="0" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="M71" s="0" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="N71" s="0" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="O71" s="0" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="D72" s="0">
         <v>2</v>
@@ -4744,42 +4780,42 @@
         <v>37</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="H72" s="0" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="I72" s="0" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="J72" s="0" t="s">
+        <v>394</v>
+      </c>
+      <c r="K72" s="0" t="s">
+        <v>395</v>
+      </c>
+      <c r="L72" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="M72" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="N72" s="0" t="s">
+        <v>396</v>
+      </c>
+      <c r="O72" s="0" t="s">
         <v>397</v>
-      </c>
-      <c r="K72" s="0" t="s">
-        <v>398</v>
-      </c>
-      <c r="L72" s="0" t="s">
-        <v>139</v>
-      </c>
-      <c r="M72" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="N72" s="0" t="s">
-        <v>399</v>
-      </c>
-      <c r="O72" s="0" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="D73" s="0">
         <v>2</v>
@@ -4791,42 +4827,42 @@
         <v>37</v>
       </c>
       <c r="G73" s="0" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="J73" s="0" t="s">
+        <v>400</v>
+      </c>
+      <c r="K73" s="0" t="s">
         <v>401</v>
       </c>
-      <c r="K73" s="0" t="s">
-        <v>402</v>
-      </c>
       <c r="L73" s="0" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="M73" s="0" t="s">
         <v>66</v>
       </c>
       <c r="N73" s="0" t="s">
+        <v>402</v>
+      </c>
+      <c r="O73" s="0" t="s">
         <v>403</v>
-      </c>
-      <c r="O73" s="0" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="D74" s="0">
         <v>2</v>
@@ -4838,13 +4874,13 @@
         <v>37</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H74" s="0" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="J74" s="0" t="s">
         <v>405</v>
@@ -4867,13 +4903,13 @@
     </row>
     <row r="75">
       <c r="A75" s="0" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="D75" s="0">
         <v>2</v>
@@ -4885,13 +4921,13 @@
         <v>37</v>
       </c>
       <c r="G75" s="0" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="H75" s="0" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="J75" s="0" t="s">
         <v>409</v>
@@ -4900,7 +4936,7 @@
         <v>410</v>
       </c>
       <c r="L75" s="0" t="s">
-        <v>238</v>
+        <v>139</v>
       </c>
       <c r="M75" s="0" t="s">
         <v>19</v>
@@ -4914,13 +4950,13 @@
     </row>
     <row r="76">
       <c r="A76" s="0" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="D76" s="0">
         <v>2</v>
@@ -4932,13 +4968,13 @@
         <v>37</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="H76" s="0" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="J76" s="0" t="s">
         <v>413</v>
@@ -4950,7 +4986,7 @@
         <v>30</v>
       </c>
       <c r="M76" s="0" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="N76" s="0" t="s">
         <v>415</v>
@@ -4961,13 +4997,13 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="D77" s="0">
         <v>2</v>
@@ -4979,13 +5015,13 @@
         <v>37</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="J77" s="0" t="s">
         <v>417</v>
@@ -4994,10 +5030,10 @@
         <v>418</v>
       </c>
       <c r="L77" s="0" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="M77" s="0" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="N77" s="0" t="s">
         <v>419</v>
@@ -5008,13 +5044,13 @@
     </row>
     <row r="78">
       <c r="A78" s="0" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="D78" s="0">
         <v>2</v>
@@ -5026,13 +5062,13 @@
         <v>37</v>
       </c>
       <c r="G78" s="0" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="J78" s="0" t="s">
         <v>421</v>
@@ -5041,10 +5077,10 @@
         <v>422</v>
       </c>
       <c r="L78" s="0" t="s">
-        <v>48</v>
+        <v>246</v>
       </c>
       <c r="M78" s="0" t="s">
-        <v>134</v>
+        <v>19</v>
       </c>
       <c r="N78" s="0" t="s">
         <v>423</v>
@@ -5055,13 +5091,13 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="D79" s="0">
         <v>2</v>
@@ -5073,31 +5109,172 @@
         <v>37</v>
       </c>
       <c r="G79" s="0" t="s">
+        <v>398</v>
+      </c>
+      <c r="H79" s="0" t="s">
+        <v>399</v>
+      </c>
+      <c r="I79" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="J79" s="0" t="s">
         <v>425</v>
       </c>
-      <c r="H79" s="0" t="s">
+      <c r="K79" s="0" t="s">
         <v>426</v>
-      </c>
-      <c r="I79" s="0" t="s">
-        <v>131</v>
-      </c>
-      <c r="J79" s="0" t="s">
-        <v>427</v>
-      </c>
-      <c r="K79" s="0" t="s">
-        <v>428</v>
       </c>
       <c r="L79" s="0" t="s">
         <v>30</v>
       </c>
       <c r="M79" s="0" t="s">
-        <v>238</v>
+        <v>24</v>
       </c>
       <c r="N79" s="0" t="s">
+        <v>427</v>
+      </c>
+      <c r="O79" s="0" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0" t="s">
+        <v>391</v>
+      </c>
+      <c r="B80" s="0" t="s">
+        <v>163</v>
+      </c>
+      <c r="C80" s="0" t="s">
+        <v>392</v>
+      </c>
+      <c r="D80" s="0">
+        <v>2</v>
+      </c>
+      <c r="E80" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="F80" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="G80" s="0" t="s">
+        <v>181</v>
+      </c>
+      <c r="H80" s="0" t="s">
+        <v>404</v>
+      </c>
+      <c r="I80" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="J80" s="0" t="s">
         <v>429</v>
       </c>
-      <c r="O79" s="0" t="s">
+      <c r="K80" s="0" t="s">
         <v>430</v>
+      </c>
+      <c r="L80" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="M80" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="N80" s="0" t="s">
+        <v>431</v>
+      </c>
+      <c r="O80" s="0" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0" t="s">
+        <v>391</v>
+      </c>
+      <c r="B81" s="0" t="s">
+        <v>177</v>
+      </c>
+      <c r="C81" s="0" t="s">
+        <v>392</v>
+      </c>
+      <c r="D81" s="0">
+        <v>2</v>
+      </c>
+      <c r="E81" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="F81" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="G81" s="0" t="s">
+        <v>314</v>
+      </c>
+      <c r="H81" s="0" t="s">
+        <v>393</v>
+      </c>
+      <c r="I81" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="J81" s="0" t="s">
+        <v>433</v>
+      </c>
+      <c r="K81" s="0" t="s">
+        <v>434</v>
+      </c>
+      <c r="L81" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="M81" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="N81" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="O81" s="0" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="0" t="s">
+        <v>391</v>
+      </c>
+      <c r="B82" s="0" t="s">
+        <v>279</v>
+      </c>
+      <c r="C82" s="0" t="s">
+        <v>392</v>
+      </c>
+      <c r="D82" s="0">
+        <v>2</v>
+      </c>
+      <c r="E82" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="F82" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="G82" s="0" t="s">
+        <v>437</v>
+      </c>
+      <c r="H82" s="0" t="s">
+        <v>438</v>
+      </c>
+      <c r="I82" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="J82" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="K82" s="0" t="s">
+        <v>440</v>
+      </c>
+      <c r="L82" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="M82" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="N82" s="0" t="s">
+        <v>441</v>
+      </c>
+      <c r="O82" s="0" t="s">
+        <v>442</v>
       </c>
     </row>
   </sheetData>
